--- a/content/Question Bank/MCQ/Python/Unit 5 - Strings/Unit 5 - Strings - MCQ.xlsx
+++ b/content/Question Bank/MCQ/Python/Unit 5 - Strings/Unit 5 - Strings - MCQ.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Python - MCQ - 5" sheetId="1" r:id="R9879aa068a4c4790"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Python - MCQ - 5" sheetId="1" r:id="Rb7b26812d3354fed"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -701,13 +701,13 @@
         <x:v>`strip()` removes the outer spaces, `lower()` produces `"red blue"`, and `split()` makes `['red', 'blue']`. Joining those pieces with `-` produces `red-blue`.</x:v>
       </x:c>
       <x:c r="D6" t="n">
-        <x:v>10</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="E6" t="str">
         <x:v>published</x:v>
       </x:c>
       <x:c r="F6" t="str">
-        <x:v>hard</x:v>
+        <x:v>medium</x:v>
       </x:c>
       <x:c r="G6" t="str">
         <x:v>analyze</x:v>
@@ -752,13 +752,13 @@
         <x:v>The input must first be normalised with `strip()` and `lower()`. Testing the cleaned value for `@` and a `.com` ending then succeeds. Checking the raw value would fail `endswith(".com")` because of its trailing spaces.</x:v>
       </x:c>
       <x:c r="D7" t="n">
-        <x:v>10</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="E7" t="str">
         <x:v>published</x:v>
       </x:c>
       <x:c r="F7" t="str">
-        <x:v>hard</x:v>
+        <x:v>medium</x:v>
       </x:c>
       <x:c r="G7" t="str">
         <x:v>analyze</x:v>
@@ -973,13 +973,13 @@
         <x:v>`sentence.lower()` is `"fox alert"`. Version A searches for lowercase `"fox"` and prints True. Version B searches for `"Fox"` with a capital F in lowercase text, so it prints False.</x:v>
       </x:c>
       <x:c r="D11" t="n">
-        <x:v>10</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="E11" t="str">
         <x:v>published</x:v>
       </x:c>
       <x:c r="F11" t="str">
-        <x:v>hard</x:v>
+        <x:v>medium</x:v>
       </x:c>
       <x:c r="G11" t="str">
         <x:v>analyze</x:v>
@@ -2194,13 +2194,13 @@
         <x:v>In the normal string, `\n` becomes one newline character, so its length is 1. In the raw string, the backslash and `n` stay as two separate characters, so its length is 2.</x:v>
       </x:c>
       <x:c r="D33" t="n">
-        <x:v>10</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="E33" t="str">
         <x:v>published</x:v>
       </x:c>
       <x:c r="F33" t="str">
-        <x:v>hard</x:v>
+        <x:v>medium</x:v>
       </x:c>
       <x:c r="G33" t="str">
         <x:v>analyze</x:v>
@@ -2251,13 +2251,13 @@
         <x:v>The cleaned text is `"red blue"`. Splitting produces two words, while removing its one space leaves `"redblue"`, which has 7 characters. The program prints 2, then 7.</x:v>
       </x:c>
       <x:c r="D34" t="n">
-        <x:v>10</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="E34" t="str">
         <x:v>published</x:v>
       </x:c>
       <x:c r="F34" t="str">
-        <x:v>hard</x:v>
+        <x:v>medium</x:v>
       </x:c>
       <x:c r="G34" t="str">
         <x:v>analyze</x:v>
@@ -2367,13 +2367,13 @@
         <x:v>`" 25 "` contains spaces, so its direct `isdigit()` result is False. After `strip()`, it becomes `"25"`, whose characters are all digits. The other invalid choices still contain non-digits or no characters.</x:v>
       </x:c>
       <x:c r="D36" t="n">
-        <x:v>10</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="E36" t="str">
         <x:v>published</x:v>
       </x:c>
       <x:c r="F36" t="str">
-        <x:v>hard</x:v>
+        <x:v>medium</x:v>
       </x:c>
       <x:c r="G36" t="str">
         <x:v>analyze</x:v>
@@ -2637,13 +2637,13 @@
         <x:v>No. Version A removes the outer spaces before removing the comma and lower-casing, so it produces `"ab"`. Version B never strips the outer spaces, so it produces `"  ab  "`.</x:v>
       </x:c>
       <x:c r="D41" t="n">
-        <x:v>10</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="E41" t="str">
         <x:v>published</x:v>
       </x:c>
       <x:c r="F41" t="str">
-        <x:v>hard</x:v>
+        <x:v>medium</x:v>
       </x:c>
       <x:c r="G41" t="str">
         <x:v>analyze</x:v>

--- a/content/Question Bank/MCQ/Python/Unit 5 - Strings/Unit 5 - Strings - MCQ.xlsx
+++ b/content/Question Bank/MCQ/Python/Unit 5 - Strings/Unit 5 - Strings - MCQ.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Python - MCQ - 5" sheetId="1" r:id="Rb7b26812d3354fed"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Python - MCQ - 5" sheetId="1" r:id="Rc0f30f7b4b7146ba"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -369,119 +369,80 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="18" customHeight="1">
-      <x:c r="A1" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">title</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B1" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">description</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C1" s="5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">explanation</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D1" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">score</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E1" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">status</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F1" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">difficulty</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G1" s="5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">bloomTaxonomy</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H1" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">tags</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I1" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">subjects</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="J1" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">topics</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="K1" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">subTopics</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="L1" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">companies</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="M1" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">option1</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="N1" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">option2</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="O1" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">option3</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="P1" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">option4</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="Q1" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">answer</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="2" ht="18" customHeight="1">
+      <x:c r="A1" s="1" t="str">
+        <x:v>title</x:v>
+      </x:c>
+      <x:c r="B1" s="1" t="str">
+        <x:v>description</x:v>
+      </x:c>
+      <x:c r="C1" s="5" t="str">
+        <x:v>explanation</x:v>
+      </x:c>
+      <x:c r="D1" s="3" t="str">
+        <x:v>score</x:v>
+      </x:c>
+      <x:c r="E1" s="1" t="str">
+        <x:v>status</x:v>
+      </x:c>
+      <x:c r="F1" s="1" t="str">
+        <x:v>difficulty</x:v>
+      </x:c>
+      <x:c r="G1" s="5" t="str">
+        <x:v>bloomTaxonomy</x:v>
+      </x:c>
+      <x:c r="H1" s="1" t="str">
+        <x:v>tags</x:v>
+      </x:c>
+      <x:c r="I1" s="1" t="str">
+        <x:v>subjects</x:v>
+      </x:c>
+      <x:c r="J1" s="1" t="str">
+        <x:v>topics</x:v>
+      </x:c>
+      <x:c r="K1" s="1" t="str">
+        <x:v>subTopics</x:v>
+      </x:c>
+      <x:c r="L1" s="1" t="str">
+        <x:v>companies</x:v>
+      </x:c>
+      <x:c r="M1" s="1" t="str">
+        <x:v>option1</x:v>
+      </x:c>
+      <x:c r="N1" s="1" t="str">
+        <x:v>option2</x:v>
+      </x:c>
+      <x:c r="O1" s="1" t="str">
+        <x:v>option3</x:v>
+      </x:c>
+      <x:c r="P1" s="1" t="str">
+        <x:v>option4</x:v>
+      </x:c>
+      <x:c r="Q1" s="3" t="str">
+        <x:v>answer</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A2" t="str">
         <x:v>Python - MCQ - 5.1.1</x:v>
       </x:c>
       <x:c r="B2" t="str">
-        <x:v>A customer database should store a trimmed, lowercase email, but the original value is still printed:
-```python
-email = "  ASHA@MAIL.COM  "
-email.strip().lower()
-print(email)
-```
-What is the smallest correct repair?</x:v>
+        <x:v>A craft-shop owner is storing a brand name that contains an apostrophe and must not break the Python literal.
+The stored text must be exactly `Meera's Crafts`. Select the simplest valid literal.</x:v>
       </x:c>
       <x:c r="C2" t="str">
-        <x:v>Both methods return new strings; neither changes `email` in place. The chained result must be stored with `email = email.strip().lower()`. That reassigns the variable to `"asha@mail.com"`.</x:v>
+        <x:v>Double quotes safely delimit text that contains an apostrophe.</x:v>
       </x:c>
       <x:c r="D2" t="n">
-        <x:v>8</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E2" t="str">
         <x:v>published</x:v>
       </x:c>
       <x:c r="F2" t="str">
-        <x:v>medium</x:v>
+        <x:v>easy</x:v>
       </x:c>
       <x:c r="G2" t="str">
-        <x:v>analyze</x:v>
+        <x:v>evaluate</x:v>
       </x:c>
       <x:c r="H2" t="str">
         <x:v>python - Set 1</x:v>
@@ -493,51 +454,50 @@
         <x:v>strings</x:v>
       </x:c>
       <x:c r="K2" t="str">
-        <x:v>common-string-methods</x:v>
+        <x:v>string-basics</x:v>
       </x:c>
       <x:c r="L2"/>
       <x:c r="M2" t="str">
-        <x:v>Call `email.lower().strip()` without storing it</x:v>
+        <x:v>`shop = 'Meera's Crafts'`</x:v>
       </x:c>
       <x:c r="N2" t="str">
-        <x:v>Use `email = email.strip().lower()`</x:v>
+        <x:v>`shop = "Meera's Crafts"`</x:v>
       </x:c>
       <x:c r="O2" t="str">
-        <x:v>Use `email[0] = email[0].lower()`</x:v>
+        <x:v>`shop = Meera's Crafts`</x:v>
       </x:c>
       <x:c r="P2" t="str">
-        <x:v>Move `print(email)` before the methods</x:v>
+        <x:v>`shop = "Meera"s Crafts"`</x:v>
       </x:c>
       <x:c r="Q2" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
-    <x:row r="3" ht="18" customHeight="1">
+    <x:row r="3" ht="132" hidden="0" customHeight="1">
       <x:c r="A3" t="str">
         <x:v>Python - MCQ - 5.1.2</x:v>
       </x:c>
       <x:c r="B3" t="str">
-        <x:v>A campaign filter incorrectly treats the number returned by `find()` as a yes/no value:
-```python
-message = input("Message: ")
-if message.find("sale"):
-    print("Tag found")
-else:
-    print("Tag missing")
+        <x:v>A product-code parser reads the first and last characters of a five-letter code before requesting one additional position.
+```python
+word = "Craft"
+first = word[0]
+last = word[-1]
+extra = word[5]
 ```
-Which input makes it print `Tag missing` even though `sale` is present?</x:v>
+Record the outcome of the third assignment.</x:v>
       </x:c>
       <x:c r="C3" t="str">
-        <x:v>For `"sale starts now"`, `find("sale")` returns 0 because the match begins at the first character. Zero is falsy, so the `else` runs incorrectly. A safe check is `"sale" in message` or `message.find("sale") != -1`.</x:v>
+        <x:v>A five-character string has valid positive indices 0 through 4.</x:v>
       </x:c>
       <x:c r="D3" t="n">
-        <x:v>10</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="E3" t="str">
         <x:v>published</x:v>
       </x:c>
       <x:c r="F3" t="str">
-        <x:v>hard</x:v>
+        <x:v>medium</x:v>
       </x:c>
       <x:c r="G3" t="str">
         <x:v>analyze</x:v>
@@ -552,51 +512,51 @@
         <x:v>strings</x:v>
       </x:c>
       <x:c r="K3" t="str">
-        <x:v>searching-within-strings</x:v>
+        <x:v>indexing-and-slicing</x:v>
       </x:c>
       <x:c r="L3"/>
       <x:c r="M3" t="str">
-        <x:v>`big sale today`</x:v>
+        <x:v>`extra` becomes `"t"`.</x:v>
       </x:c>
       <x:c r="N3" t="str">
-        <x:v>`flash sale`</x:v>
+        <x:v>`extra` becomes `""`.</x:v>
       </x:c>
       <x:c r="O3" t="str">
-        <x:v>`presale notice`</x:v>
+        <x:v>`extra` becomes `None`.</x:v>
       </x:c>
       <x:c r="P3" t="str">
-        <x:v>`sale starts now`</x:v>
+        <x:v>Python raises `IndexError` because index 5 does not exist.</x:v>
       </x:c>
       <x:c r="Q3" t="n">
         <x:v>4</x:v>
       </x:c>
     </x:row>
-    <x:row r="4">
+    <x:row r="4" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A4" t="str">
         <x:v>Python - MCQ - 5.1.3</x:v>
       </x:c>
       <x:c r="B4" t="str">
-        <x:v>A warehouse code must change from `A123` to `B123`. Direct assignment fails because strings are immutable:
-```python
-code = "A123"
-code[0] = "B"
+        <x:v>A username was saved with the wrong first letter, and the developer must correct it without editing a string in place.
+```python
+username = "neera"
+username[0] = "m"
 ```
-Which replacement builds the required new string?</x:v>
+Approve the smallest repair that creates `"meera"` without item assignment.</x:v>
       </x:c>
       <x:c r="C4" t="str">
-        <x:v>The suffix `code[1:]` is `"123"`. Placing `"B"` in front creates the new string `"B123"`, which can be reassigned to `code`. No character is edited in place.</x:v>
+        <x:v>Strings are immutable; slicing and concatenation build a new string that can be reassigned.</x:v>
       </x:c>
       <x:c r="D4" t="n">
-        <x:v>8</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E4" t="str">
         <x:v>published</x:v>
       </x:c>
       <x:c r="F4" t="str">
-        <x:v>medium</x:v>
+        <x:v>hard</x:v>
       </x:c>
       <x:c r="G4" t="str">
-        <x:v>apply</x:v>
+        <x:v>evaluate</x:v>
       </x:c>
       <x:c r="H4" t="str">
         <x:v>python - Set 1</x:v>
@@ -608,39 +568,40 @@
         <x:v>strings</x:v>
       </x:c>
       <x:c r="K4" t="str">
-        <x:v>string-immutability</x:v>
+        <x:v>string-basics</x:v>
       </x:c>
       <x:c r="L4"/>
       <x:c r="M4" t="str">
-        <x:v>`code = "B" + code[1:]`</x:v>
+        <x:v>`username = "m" + username[1:]`</x:v>
       </x:c>
       <x:c r="N4" t="str">
-        <x:v>`code[1] = "B"`</x:v>
+        <x:v>`username[0].replace("n", "m")`</x:v>
       </x:c>
       <x:c r="O4" t="str">
-        <x:v>`code = code[1:] + "B"`</x:v>
+        <x:v>`username[0] == "m"`</x:v>
       </x:c>
       <x:c r="P4" t="str">
-        <x:v>`code = "B" + code`</x:v>
+        <x:v>`username.insert(0, "m")`</x:v>
       </x:c>
       <x:c r="Q4" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="5">
+    <x:row r="5" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A5" t="str">
         <x:v>Python - MCQ - 5.1.4</x:v>
       </x:c>
       <x:c r="B5" t="str">
-        <x:v>A product code is `IN-4827-RED`. A label needs only the four digits `4827`:
-```python
-code = "IN-4827-RED"
-digits = ________
+        <x:v>A marketplace receives comma-separated tags and must rebuild the cleaned pieces as one hyphenated slug.
+```python
+tags = "craft, gifts, pune"
+pieces = tags.split(", ")
+hashtag = __________
 ```
-Which slice is correct?</x:v>
+The final value must be `"craft-gifts-pune"`.</x:v>
       </x:c>
       <x:c r="C5" t="str">
-        <x:v>The digits begin at index 3 and occupy indexes 3, 4, 5, and 6. Because a slice excludes its stop index, `code[3:7]` returns exactly `"4827"`.</x:v>
+        <x:v>The separator calls `join()` on the collection of string pieces.</x:v>
       </x:c>
       <x:c r="D5" t="n">
         <x:v>8</x:v>
@@ -664,53 +625,47 @@
         <x:v>strings</x:v>
       </x:c>
       <x:c r="K5" t="str">
-        <x:v>indexing-and-slicing</x:v>
+        <x:v>split-and-join</x:v>
       </x:c>
       <x:c r="L5"/>
       <x:c r="M5" t="str">
-        <x:v>`code[0:4]`</x:v>
+        <x:v>`pieces.join("-")`</x:v>
       </x:c>
       <x:c r="N5" t="str">
-        <x:v>`code[3:8]`</x:v>
+        <x:v>`tags.join(pieces)`</x:v>
       </x:c>
       <x:c r="O5" t="str">
-        <x:v>`code[3:7]`</x:v>
+        <x:v>`"-".join(pieces)`</x:v>
       </x:c>
       <x:c r="P5" t="str">
-        <x:v>`code[-3:]`</x:v>
+        <x:v>`pieces.split("-")`</x:v>
       </x:c>
       <x:c r="Q5" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>
-    <x:row r="6">
+    <x:row r="6" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A6" t="str">
         <x:v>Python - MCQ - 5.1.5</x:v>
       </x:c>
       <x:c r="B6" t="str">
-        <x:v>A publishing tool turns a title into a URL slug:
-```python
-raw = "  Red Blue  "
-words = raw.strip().lower().split()
-slug = "-".join(words)
-print(slug)
-```
-What is printed?</x:v>
+        <x:v>A caption analyser searches for an optional coupon code that may legitimately be absent.
+An optional coupon code may be absent from a caption. The program needs its first position when present and a non-crashing sentinel when absent. Select the correct operation.</x:v>
       </x:c>
       <x:c r="C6" t="str">
-        <x:v>`strip()` removes the outer spaces, `lower()` produces `"red blue"`, and `split()` makes `['red', 'blue']`. Joining those pieces with `-` produces `red-blue`.</x:v>
+        <x:v>`find()` reports the first index or `-1`; `index()` raises an error when the text is missing.</x:v>
       </x:c>
       <x:c r="D6" t="n">
-        <x:v>8</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E6" t="str">
         <x:v>published</x:v>
       </x:c>
       <x:c r="F6" t="str">
-        <x:v>medium</x:v>
+        <x:v>hard</x:v>
       </x:c>
       <x:c r="G6" t="str">
-        <x:v>analyze</x:v>
+        <x:v>evaluate</x:v>
       </x:c>
       <x:c r="H6" t="str">
         <x:v>python - Set 1</x:v>
@@ -722,46 +677,51 @@
         <x:v>strings</x:v>
       </x:c>
       <x:c r="K6" t="str">
-        <x:v>splitting-and-joining</x:v>
+        <x:v>searching-and-membership</x:v>
       </x:c>
       <x:c r="L6"/>
       <x:c r="M6" t="str">
-        <x:v>`Red-Blue`</x:v>
+        <x:v>`caption.index(code)` because it returns zero when absent</x:v>
       </x:c>
       <x:c r="N6" t="str">
-        <x:v>`red-blue`</x:v>
+        <x:v>`caption.count(code)` because it returns the position</x:v>
       </x:c>
       <x:c r="O6" t="str">
-        <x:v>`red blue`</x:v>
+        <x:v>`caption.find(code)` because it returns `-1` when absent</x:v>
       </x:c>
       <x:c r="P6" t="str">
-        <x:v>`-red-blue-`</x:v>
+        <x:v>`code in caption` because it returns the position</x:v>
       </x:c>
       <x:c r="Q6" t="n">
-        <x:v>2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A7" t="str">
         <x:v>Python - MCQ - 5.1.6</x:v>
       </x:c>
       <x:c r="B7" t="str">
-        <x:v>A signup form should ignore outer spaces and capitalisation before doing a rough email check. Which version correctly handles the input `"  ASHA@MAIL.COM  "`?</x:v>
+        <x:v>A shop price list must display every amount with exactly two decimal places.
+```python
+price = 49.5
+display = f"₹{price:_____}"
+```
+The required display is `₹49.50`.</x:v>
       </x:c>
       <x:c r="C7" t="str">
-        <x:v>The input must first be normalised with `strip()` and `lower()`. Testing the cleaned value for `@` and a `.com` ending then succeeds. Checking the raw value would fail `endswith(".com")` because of its trailing spaces.</x:v>
+        <x:v>`.2f` formats a numeric value with exactly two decimal places.</x:v>
       </x:c>
       <x:c r="D7" t="n">
-        <x:v>8</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E7" t="str">
         <x:v>published</x:v>
       </x:c>
       <x:c r="F7" t="str">
-        <x:v>medium</x:v>
+        <x:v>easy</x:v>
       </x:c>
       <x:c r="G7" t="str">
-        <x:v>analyze</x:v>
+        <x:v>apply</x:v>
       </x:c>
       <x:c r="H7" t="str">
         <x:v>python - Set 1</x:v>
@@ -773,48 +733,49 @@
         <x:v>strings</x:v>
       </x:c>
       <x:c r="K7" t="str">
-        <x:v>practical-text-processing</x:v>
+        <x:v>string-formatting</x:v>
       </x:c>
       <x:c r="L7"/>
       <x:c r="M7" t="str">
-        <x:v>`clean = raw.strip().lower()` then test `"@" in clean and clean.endswith(".com")`</x:v>
+        <x:v>`.2f`</x:v>
       </x:c>
       <x:c r="N7" t="str">
-        <x:v>Test `"@" in raw and raw.endswith(".com")` before cleaning</x:v>
+        <x:v>`2`</x:v>
       </x:c>
       <x:c r="O7" t="str">
-        <x:v>Test `raw.find("@") and raw.startswith(".com")`</x:v>
+        <x:v>`.2%`</x:v>
       </x:c>
       <x:c r="P7" t="str">
-        <x:v>Use `raw.upper()` and test whether it starts with `@`</x:v>
+        <x:v>`,`</x:v>
       </x:c>
       <x:c r="Q7" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="8">
+    <x:row r="8" ht="132" hidden="0" customHeight="1">
       <x:c r="A8" t="str">
         <x:v>Python - MCQ - 5.1.7</x:v>
       </x:c>
       <x:c r="B8" t="str">
-        <x:v>A progress dashboard stores completion as a proportion:
-```python
-completion = 0.075
-print(f"{completion:.1%}")
+        <x:v>A status panel needs two output lines and must preserve quotation marks around the readiness message.
+The output must be:
+```text
+Status
+"Ready"
 ```
-What appears?</x:v>
+Select the valid one-line string literal.</x:v>
       </x:c>
       <x:c r="C8" t="str">
-        <x:v>The `.1%` format multiplies the proportion by 100, adds the percent sign, and keeps one decimal place. `0.075` therefore displays as `7.5%`.</x:v>
+        <x:v>`\n` inserts the line break and `\"` preserves the double quotes inside the literal.</x:v>
       </x:c>
       <x:c r="D8" t="n">
-        <x:v>5</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="E8" t="str">
         <x:v>published</x:v>
       </x:c>
       <x:c r="F8" t="str">
-        <x:v>easy</x:v>
+        <x:v>medium</x:v>
       </x:c>
       <x:c r="G8" t="str">
         <x:v>apply</x:v>
@@ -829,46 +790,47 @@
         <x:v>strings</x:v>
       </x:c>
       <x:c r="K8" t="str">
-        <x:v>string-formatting-and-fstrings</x:v>
+        <x:v>escape-sequences</x:v>
       </x:c>
       <x:c r="L8"/>
       <x:c r="M8" t="str">
-        <x:v>`0.1%`</x:v>
+        <x:v>`message = "Status/n"Ready""`</x:v>
       </x:c>
       <x:c r="N8" t="str">
-        <x:v>`0.075%`</x:v>
+        <x:v>`message = "Status\tReady"`</x:v>
       </x:c>
       <x:c r="O8" t="str">
-        <x:v>`75.0%`</x:v>
+        <x:v>`message = "Status"\n"Ready""`</x:v>
       </x:c>
       <x:c r="P8" t="str">
-        <x:v>`7.5%`</x:v>
+        <x:v>`message = "Status\n\"Ready\""`</x:v>
       </x:c>
       <x:c r="Q8" t="n">
         <x:v>4</x:v>
       </x:c>
     </x:row>
-    <x:row r="9">
+    <x:row r="9" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A9" t="str">
         <x:v>Python - MCQ - 5.1.8</x:v>
       </x:c>
       <x:c r="B9" t="str">
-        <x:v>A Windows path must display exactly as `C:\new\table`. In a normal string, `\n` and `\t` are being treated as escape sequences. Which smallest change preserves the backslashes?</x:v>
+        <x:v>A marketplace import contains outer spaces, inconsistent capitalisation, and comma-separated categories.
+Input arrives as `"  PYTHON, CRAFTS  "`. The required pieces are `['python', 'crafts']`. Which pipeline performs the operations in a sensible order?</x:v>
       </x:c>
       <x:c r="C9" t="str">
-        <x:v>Adding the `r` prefix creates a raw string, so the backslashes are treated literally rather than as newline and tab codes. `r"C:\new\table"` displays the required path.</x:v>
+        <x:v>Cleaning and normalising the string before splitting produces two lowercase pieces without outer whitespace.</x:v>
       </x:c>
       <x:c r="D9" t="n">
-        <x:v>8</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E9" t="str">
         <x:v>published</x:v>
       </x:c>
       <x:c r="F9" t="str">
-        <x:v>medium</x:v>
+        <x:v>hard</x:v>
       </x:c>
       <x:c r="G9" t="str">
-        <x:v>apply</x:v>
+        <x:v>evaluate</x:v>
       </x:c>
       <x:c r="H9" t="str">
         <x:v>python - Set 1</x:v>
@@ -880,39 +842,38 @@
         <x:v>strings</x:v>
       </x:c>
       <x:c r="K9" t="str">
-        <x:v>escape-sequences-and-multiline-strings</x:v>
+        <x:v>text-processing</x:v>
       </x:c>
       <x:c r="L9"/>
       <x:c r="M9" t="str">
-        <x:v>Use `f"C:\new\table"`</x:v>
+        <x:v>Split on commas, then call `.lower()` on the resulting list.</x:v>
       </x:c>
       <x:c r="N9" t="str">
-        <x:v>Use a triple-quoted normal string</x:v>
+        <x:v>Strip the text, lower it, then split on `", "`.</x:v>
       </x:c>
       <x:c r="O9" t="str">
-        <x:v>Use `r"C:\new\table"`</x:v>
+        <x:v>Join the original text, then strip the list.</x:v>
       </x:c>
       <x:c r="P9" t="str">
-        <x:v>Call `.strip()` on the path</x:v>
+        <x:v>Find the comma, discard everything after it, then uppercase.</x:v>
       </x:c>
       <x:c r="Q9" t="n">
-        <x:v>3</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="79.19999694824219" hidden="0" customHeight="1">
       <x:c r="A10" t="str">
         <x:v>Python - MCQ - 5.1.9</x:v>
       </x:c>
       <x:c r="B10" t="str">
-        <x:v>A parcel code must contain exactly five characters. The code is `"AB 12"`, with one space in the middle:
-```python
-code = "AB 12"
-print(len(code))
-```
-What is printed?</x:v>
+        <x:v>A payment-confirmation screen reveals only the final four digits of a stored phone number.
+```python
+phone = "9876543210"
+last_four = __________
+```</x:v>
       </x:c>
       <x:c r="C10" t="str">
-        <x:v>A space is a character in a string. The sequence is `A`, `B`, space, `1`, `2`, so `len(code)` is 5.</x:v>
+        <x:v>A start of `-4` counts from the end, and an omitted stop continues through the final character.</x:v>
       </x:c>
       <x:c r="D10" t="n">
         <x:v>5</x:v>
@@ -924,7 +885,7 @@
         <x:v>easy</x:v>
       </x:c>
       <x:c r="G10" t="str">
-        <x:v>understand</x:v>
+        <x:v>apply</x:v>
       </x:c>
       <x:c r="H10" t="str">
         <x:v>python - Set 1</x:v>
@@ -936,41 +897,39 @@
         <x:v>strings</x:v>
       </x:c>
       <x:c r="K10" t="str">
-        <x:v>what-is-a-string</x:v>
+        <x:v>indexing-and-slicing</x:v>
       </x:c>
       <x:c r="L10"/>
       <x:c r="M10" t="str">
-        <x:v>5</x:v>
+        <x:v>`phone[-4:]`</x:v>
       </x:c>
       <x:c r="N10" t="str">
-        <x:v>4</x:v>
+        <x:v>`phone[4:]`</x:v>
       </x:c>
       <x:c r="O10" t="str">
-        <x:v>2</x:v>
+        <x:v>`phone[:-4]`</x:v>
       </x:c>
       <x:c r="P10" t="str">
-        <x:v>6</x:v>
+        <x:v>`phone[-1:4]`</x:v>
       </x:c>
       <x:c r="Q10" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="11">
+    <x:row r="11" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A11" t="str">
         <x:v>Python - MCQ - 5.1.10</x:v>
       </x:c>
       <x:c r="B11" t="str">
-        <x:v>Two alert checks are tested with `sentence = "FOX alert"`:
-```python
-# Version A
-print("fox" in sentence.lower())
-# Version B
-print("Fox" in sentence.lower())
+        <x:v>An email-import service must trim accidental spaces, normalise capitalisation, and retain the cleaned result.
+```python
+email = "  ASHA@EXAMPLE.COM  "
+__________
 ```
-What does each version print?</x:v>
+The variable itself must become `"asha@example.com"`.</x:v>
       </x:c>
       <x:c r="C11" t="str">
-        <x:v>`sentence.lower()` is `"fox alert"`. Version A searches for lowercase `"fox"` and prints True. Version B searches for `"Fox"` with a capital F in lowercase text, so it prints False.</x:v>
+        <x:v>Both methods return new strings, so the chained result must be reassigned.</x:v>
       </x:c>
       <x:c r="D11" t="n">
         <x:v>8</x:v>
@@ -982,7 +941,7 @@
         <x:v>medium</x:v>
       </x:c>
       <x:c r="G11" t="str">
-        <x:v>analyze</x:v>
+        <x:v>apply</x:v>
       </x:c>
       <x:c r="H11" t="str">
         <x:v>python - Set 1</x:v>
@@ -994,39 +953,38 @@
         <x:v>strings</x:v>
       </x:c>
       <x:c r="K11" t="str">
-        <x:v>searching-within-strings</x:v>
+        <x:v>string-methods</x:v>
       </x:c>
       <x:c r="L11"/>
       <x:c r="M11" t="str">
-        <x:v>Both print True</x:v>
+        <x:v>`email.strip().lower()`</x:v>
       </x:c>
       <x:c r="N11" t="str">
-        <x:v>Version A prints True; Version B prints False</x:v>
+        <x:v>`email = email.strip`</x:v>
       </x:c>
       <x:c r="O11" t="str">
-        <x:v>Version A prints False; Version B prints True</x:v>
+        <x:v>`email = email.strip().lower()`</x:v>
       </x:c>
       <x:c r="P11" t="str">
-        <x:v>Both print False</x:v>
+        <x:v>`email.lower = email.strip()`</x:v>
       </x:c>
       <x:c r="Q11" t="n">
-        <x:v>2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="79.19999694824219" hidden="0" customHeight="1">
       <x:c r="A12" t="str">
         <x:v>Python - MCQ - 5.2.1</x:v>
       </x:c>
       <x:c r="B12" t="str">
-        <x:v>A billing system needs the second-to-last character of an invoice label:
-```python
-label = "invoice"
-print(label[-2])
-```
-What is printed?</x:v>
+        <x:v>A profile form counts every character in a short greeting, including the space between words.
+```python
+text = "Hi all"
+size = len(text)
+```</x:v>
       </x:c>
       <x:c r="C12" t="str">
-        <x:v>Negative indexes count from the end: `-1` is `e`, so `-2` is the preceding character, `c`.</x:v>
+        <x:v>Two letters, one space, and three more letters make six characters.</x:v>
       </x:c>
       <x:c r="D12" t="n">
         <x:v>5</x:v>
@@ -1038,7 +996,7 @@
         <x:v>easy</x:v>
       </x:c>
       <x:c r="G12" t="str">
-        <x:v>understand</x:v>
+        <x:v>apply</x:v>
       </x:c>
       <x:c r="H12" t="str">
         <x:v>python - Set 2</x:v>
@@ -1050,39 +1008,35 @@
         <x:v>strings</x:v>
       </x:c>
       <x:c r="K12" t="str">
-        <x:v>indexing-and-slicing</x:v>
+        <x:v>string-basics</x:v>
       </x:c>
       <x:c r="L12"/>
       <x:c r="M12" t="str">
-        <x:v>`i`</x:v>
+        <x:v>`4`</x:v>
       </x:c>
       <x:c r="N12" t="str">
-        <x:v>`e`</x:v>
+        <x:v>`5`</x:v>
       </x:c>
       <x:c r="O12" t="str">
-        <x:v>`c`</x:v>
+        <x:v>`7`</x:v>
       </x:c>
       <x:c r="P12" t="str">
-        <x:v>`o`</x:v>
+        <x:v>`6`</x:v>
       </x:c>
       <x:c r="Q12" t="n">
-        <x:v>3</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A13" t="str">
         <x:v>Python - MCQ - 5.2.2</x:v>
       </x:c>
       <x:c r="B13" t="str">
-        <x:v>A code reader takes every second character from part of a string:
-```python
-text = "ABCDEFGH"
-print(text[1:7:2])
-```
-Which text is produced?</x:v>
+        <x:v>A coupon service extracts a middle section of a code and must respect Python's exclusive slice boundary.
+For `word = "Python"`, complete the map: `word[1:4]` selects indices _____ and produces _____.</x:v>
       </x:c>
       <x:c r="C13" t="str">
-        <x:v>The slice starts at index 1 and steps by 2 while staying before index 7. It takes indexes 1, 3, and 5: `B`, `D`, and `F`, producing `BDF`.</x:v>
+        <x:v>Slicing includes the start index and excludes the stop index.</x:v>
       </x:c>
       <x:c r="D13" t="n">
         <x:v>8</x:v>
@@ -1094,7 +1048,7 @@
         <x:v>medium</x:v>
       </x:c>
       <x:c r="G13" t="str">
-        <x:v>analyze</x:v>
+        <x:v>apply</x:v>
       </x:c>
       <x:c r="H13" t="str">
         <x:v>python - Set 2</x:v>
@@ -1110,35 +1064,34 @@
       </x:c>
       <x:c r="L13"/>
       <x:c r="M13" t="str">
-        <x:v>`BDF`</x:v>
+        <x:v>`1, 2, 3, 4`; `"ytho"`</x:v>
       </x:c>
       <x:c r="N13" t="str">
-        <x:v>`ACEG`</x:v>
+        <x:v>`1, 2, 3`; `"yth"`</x:v>
       </x:c>
       <x:c r="O13" t="str">
-        <x:v>`BDFH`</x:v>
+        <x:v>`0, 1, 2, 3`; `"Pyth"`</x:v>
       </x:c>
       <x:c r="P13" t="str">
-        <x:v>`BCDEFG`</x:v>
+        <x:v>`1, 4`; `"yo"`</x:v>
       </x:c>
       <x:c r="Q13" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="79.19999694824219" hidden="0" customHeight="1">
       <x:c r="A14" t="str">
         <x:v>Python - MCQ - 5.2.3</x:v>
       </x:c>
       <x:c r="B14" t="str">
-        <x:v>A slice asks for characters beyond the end of a short string:
-```python
-word = "cat"
-print(word[1:10])
-```
-What happens?</x:v>
+        <x:v>A warehouse needs a product code displayed in reverse without writing a manual loop.
+```python
+code = "ABCD"
+reversed_code = code[__________]
+```</x:v>
       </x:c>
       <x:c r="C14" t="str">
-        <x:v>Unlike a single out-of-range index, a slice safely stops at the end of the string. Starting at index 1 returns `"at"`; the stop value 10 does not cause an error.</x:v>
+        <x:v>A step of `-1` traverses the full string from end to start.</x:v>
       </x:c>
       <x:c r="D14" t="n">
         <x:v>8</x:v>
@@ -1150,7 +1103,7 @@
         <x:v>medium</x:v>
       </x:c>
       <x:c r="G14" t="str">
-        <x:v>analyze</x:v>
+        <x:v>apply</x:v>
       </x:c>
       <x:c r="H14" t="str">
         <x:v>python - Set 2</x:v>
@@ -1166,47 +1119,48 @@
       </x:c>
       <x:c r="L14"/>
       <x:c r="M14" t="str">
-        <x:v>It raises `IndexError`</x:v>
+        <x:v>`-1`</x:v>
       </x:c>
       <x:c r="N14" t="str">
-        <x:v>It prints an empty string</x:v>
+        <x:v>`1:-1`</x:v>
       </x:c>
       <x:c r="O14" t="str">
-        <x:v>It prints `cat`</x:v>
+        <x:v>`::-1`</x:v>
       </x:c>
       <x:c r="P14" t="str">
-        <x:v>It prints `at`</x:v>
+        <x:v>`-1:0`</x:v>
       </x:c>
       <x:c r="Q14" t="n">
-        <x:v>4</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A15" t="str">
         <x:v>Python - MCQ - 5.2.4</x:v>
       </x:c>
       <x:c r="B15" t="str">
-        <x:v>An empty field is checked with both character-test methods:
-```python
-entry = ""
-print(entry.isdigit(), entry.isalpha())
+        <x:v>A preview service is being tested with requests that extend beyond a short word's available characters.
+```python
+word = "cat"
+one = word[10]
+two = word[:10]
 ```
-What is printed?</x:v>
+Which review statement is accurate?</x:v>
       </x:c>
       <x:c r="C15" t="str">
-        <x:v>Both methods require the string to contain characters of the requested kind. An empty string contains neither digits nor letters, so both checks return False.</x:v>
+        <x:v>A single invalid index fails, while slice boundaries are safely limited to the available string.</x:v>
       </x:c>
       <x:c r="D15" t="n">
-        <x:v>5</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E15" t="str">
         <x:v>published</x:v>
       </x:c>
       <x:c r="F15" t="str">
-        <x:v>easy</x:v>
+        <x:v>hard</x:v>
       </x:c>
       <x:c r="G15" t="str">
-        <x:v>understand</x:v>
+        <x:v>evaluate</x:v>
       </x:c>
       <x:c r="H15" t="str">
         <x:v>python - Set 2</x:v>
@@ -1218,40 +1172,40 @@
         <x:v>strings</x:v>
       </x:c>
       <x:c r="K15" t="str">
-        <x:v>common-string-methods</x:v>
+        <x:v>indexing-and-slicing</x:v>
       </x:c>
       <x:c r="L15"/>
       <x:c r="M15" t="str">
-        <x:v>`True True`</x:v>
+        <x:v>`word[10]` raises `IndexError`, while `word[:10]` safely returns `"cat"`.</x:v>
       </x:c>
       <x:c r="N15" t="str">
-        <x:v>`False False`</x:v>
+        <x:v>Both expressions return `""`.</x:v>
       </x:c>
       <x:c r="O15" t="str">
-        <x:v>`True False`</x:v>
+        <x:v>Both expressions raise `IndexError`.</x:v>
       </x:c>
       <x:c r="P15" t="str">
-        <x:v>`False True`</x:v>
+        <x:v>`word[10]` returns `"t"`, while the slice raises an error.</x:v>
       </x:c>
       <x:c r="Q15" t="n">
-        <x:v>2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A16" t="str">
         <x:v>Python - MCQ - 5.2.5</x:v>
       </x:c>
       <x:c r="B16" t="str">
-        <x:v>A menu editor cleans and renames every occurrence of a drink:
-```python
-text = "  tea tea  "
-result = text.replace("tea", "coffee").strip().title()
-print(result)
+        <x:v>A user-profile cleanup calls an uppercase method, but the displayed name remains unchanged.
+```python
+name = "asha"
+name.upper()
+print(name)
 ```
-What is printed?</x:v>
+Complete the reviewer note.</x:v>
       </x:c>
       <x:c r="C16" t="str">
-        <x:v>`replace` changes both copies of `tea`, `strip` removes the outer spaces, and `title` capitalises both resulting words. The final text is `Coffee Coffee`.</x:v>
+        <x:v>Transforming string methods do not mutate the original value.</x:v>
       </x:c>
       <x:c r="D16" t="n">
         <x:v>8</x:v>
@@ -1263,7 +1217,7 @@
         <x:v>medium</x:v>
       </x:c>
       <x:c r="G16" t="str">
-        <x:v>analyze</x:v>
+        <x:v>evaluate</x:v>
       </x:c>
       <x:c r="H16" t="str">
         <x:v>python - Set 2</x:v>
@@ -1275,51 +1229,50 @@
         <x:v>strings</x:v>
       </x:c>
       <x:c r="K16" t="str">
-        <x:v>common-string-methods</x:v>
+        <x:v>string-methods</x:v>
       </x:c>
       <x:c r="L16"/>
       <x:c r="M16" t="str">
-        <x:v>`coffee coffee`</x:v>
+        <x:v>`upper()` fails because lowercase text is immutable.</x:v>
       </x:c>
       <x:c r="N16" t="str">
-        <x:v>`Tea Tea`</x:v>
+        <x:v>`upper()` returned a new string that was not stored, so `name` remains `"asha"`.</x:v>
       </x:c>
       <x:c r="O16" t="str">
-        <x:v>`Coffee Coffee`</x:v>
+        <x:v>`print()` automatically converts text back to lowercase.</x:v>
       </x:c>
       <x:c r="P16" t="str">
-        <x:v>`Coffee tea`</x:v>
+        <x:v>`upper()` changes only the first character.</x:v>
       </x:c>
       <x:c r="Q16" t="n">
-        <x:v>3</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="79.19999694824219" hidden="0" customHeight="1">
       <x:c r="A17" t="str">
         <x:v>Python - MCQ - 5.2.6</x:v>
       </x:c>
       <x:c r="B17" t="str">
-        <x:v>A floor plan renames each room label:
-```python
-text = "room 101, room 102"
-print(text.replace("room", "desk"))
-```
-Which result appears?</x:v>
+        <x:v>A product catalogue replaces an old term everywhere it occurs, including inside a longer word.
+```python
+text = "tea team"
+changed = text.replace("tea", "art")
+```</x:v>
       </x:c>
       <x:c r="C17" t="str">
-        <x:v>`replace` changes every occurrence, not only the first. Both room labels become desk labels, producing `desk 101, desk 102`.</x:v>
+        <x:v>`replace()` changes every non-overlapping occurrence of `"tea"`, including the start of `"team"`.</x:v>
       </x:c>
       <x:c r="D17" t="n">
-        <x:v>8</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E17" t="str">
         <x:v>published</x:v>
       </x:c>
       <x:c r="F17" t="str">
-        <x:v>medium</x:v>
+        <x:v>easy</x:v>
       </x:c>
       <x:c r="G17" t="str">
-        <x:v>analyze</x:v>
+        <x:v>apply</x:v>
       </x:c>
       <x:c r="H17" t="str">
         <x:v>python - Set 2</x:v>
@@ -1331,40 +1284,38 @@
         <x:v>strings</x:v>
       </x:c>
       <x:c r="K17" t="str">
-        <x:v>common-string-methods</x:v>
+        <x:v>string-methods</x:v>
       </x:c>
       <x:c r="L17"/>
       <x:c r="M17" t="str">
-        <x:v>`desk 101, room 102`</x:v>
+        <x:v>`"art team"`</x:v>
       </x:c>
       <x:c r="N17" t="str">
-        <x:v>`room 101, desk 102`</x:v>
+        <x:v>`"tea artm"`</x:v>
       </x:c>
       <x:c r="O17" t="str">
-        <x:v>`room 101, room 102`</x:v>
+        <x:v>`"art"`</x:v>
       </x:c>
       <x:c r="P17" t="str">
-        <x:v>`desk 101, desk 102`</x:v>
+        <x:v>`"art artm"`</x:v>
       </x:c>
       <x:c r="Q17" t="n">
         <x:v>4</x:v>
       </x:c>
     </x:row>
-    <x:row r="18">
+    <x:row r="18" ht="79.19999694824219" hidden="0" customHeight="1">
       <x:c r="A18" t="str">
         <x:v>Python - MCQ - 5.2.7</x:v>
       </x:c>
       <x:c r="B18" t="str">
-        <x:v>A report compares two capitalisation methods:
-```python
-text = "hello WORLD"
-print(text.title())
-print(text.capitalize())
-```
-Which two lines print?</x:v>
+        <x:v>A weather form uses `.isdigit()` to inspect a signed temperature entered as text.
+```python
+raw = "-5"
+valid = raw.isdigit()
+```</x:v>
       </x:c>
       <x:c r="C18" t="str">
-        <x:v>`title()` capitalises the first letter of each word and lowers the rest, giving `Hello World`. `capitalize()` capitalises only the first character of the whole string and lowers the remaining text, giving `Hello world`.</x:v>
+        <x:v>`.isdigit()` inspects characters; the leading minus sign causes the check to return false.</x:v>
       </x:c>
       <x:c r="D18" t="n">
         <x:v>8</x:v>
@@ -1388,48 +1339,48 @@
         <x:v>strings</x:v>
       </x:c>
       <x:c r="K18" t="str">
-        <x:v>common-string-methods</x:v>
+        <x:v>string-methods</x:v>
       </x:c>
       <x:c r="L18"/>
       <x:c r="M18" t="str">
-        <x:v>`Hello World` then `Hello world`</x:v>
+        <x:v>`valid` is `False` because the minus sign is not a digit.</x:v>
       </x:c>
       <x:c r="N18" t="str">
-        <x:v>`HELLO WORLD` then `Hello WORLD`</x:v>
+        <x:v>`valid` is `True` because `-5` is numerically valid.</x:v>
       </x:c>
       <x:c r="O18" t="str">
-        <x:v>`Hello world` then `Hello World`</x:v>
+        <x:v>`.isdigit()` converts the text to integer `-5`.</x:v>
       </x:c>
       <x:c r="P18" t="str">
-        <x:v>`hello WORLD` twice</x:v>
+        <x:v>Python raises `ValueError` inside `.isdigit()`.</x:v>
       </x:c>
       <x:c r="Q18" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="19">
+    <x:row r="19" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A19" t="str">
         <x:v>Python - MCQ - 5.2.8</x:v>
       </x:c>
       <x:c r="B19" t="str">
-        <x:v>A name field allows a space between first and last names:
-```python
-name = "Asha Rao"
-print(name.isalpha())
+        <x:v>A report builder tries to join numeric identifiers with hyphens before converting them to strings.
+```python
+parts = [10, 20, 30]
+result = "-".join(parts)
 ```
-What does the check return?</x:v>
+Select the correct diagnosis.</x:v>
       </x:c>
       <x:c r="C19" t="str">
-        <x:v>`isalpha()` requires every character to be a letter. The space between the two names is not a letter, so the result is False even though all visible words contain letters.</x:v>
+        <x:v>The separator can be any string, but every joined element must already be a string.</x:v>
       </x:c>
       <x:c r="D19" t="n">
-        <x:v>8</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E19" t="str">
         <x:v>published</x:v>
       </x:c>
       <x:c r="F19" t="str">
-        <x:v>medium</x:v>
+        <x:v>hard</x:v>
       </x:c>
       <x:c r="G19" t="str">
         <x:v>analyze</x:v>
@@ -1444,41 +1395,35 @@
         <x:v>strings</x:v>
       </x:c>
       <x:c r="K19" t="str">
-        <x:v>common-string-methods</x:v>
+        <x:v>split-and-join</x:v>
       </x:c>
       <x:c r="L19"/>
       <x:c r="M19" t="str">
-        <x:v>True, because both words contain letters</x:v>
+        <x:v>The hyphen cannot be used as a separator.</x:v>
       </x:c>
       <x:c r="N19" t="str">
-        <x:v>False, because the space is not a letter</x:v>
+        <x:v>`join()` works only with an empty separator.</x:v>
       </x:c>
       <x:c r="O19" t="str">
-        <x:v>8, the number of letters</x:v>
+        <x:v>`join()` requires string pieces, but the collection contains integers.</x:v>
       </x:c>
       <x:c r="P19" t="str">
-        <x:v>An error, because names cannot contain spaces</x:v>
+        <x:v>The list must contain exactly two items.</x:v>
       </x:c>
       <x:c r="Q19" t="n">
-        <x:v>2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A20" t="str">
         <x:v>Python - MCQ - 5.2.9</x:v>
       </x:c>
       <x:c r="B20" t="str">
-        <x:v>A cleanup stores only the result of `strip()`:
-```python
-raw = "  MiXeD  "
-clean = raw.strip()
-raw.lower()
-print(clean)
-```
-What is printed?</x:v>
+        <x:v>A caption parser must treat several consecutive spaces as one word boundary.
+The text is `"red   blue"` with three spaces. Which statement is correct?</x:v>
       </x:c>
       <x:c r="C20" t="str">
-        <x:v>`clean` receives the trimmed value `"MiXeD"`. The later `raw.lower()` result is not stored and does not affect `clean`. Therefore the mixed capitalisation remains.</x:v>
+        <x:v>Default splitting treats runs of whitespace as separators; an explicit single space cuts at each individual space.</x:v>
       </x:c>
       <x:c r="D20" t="n">
         <x:v>8</x:v>
@@ -1502,51 +1447,52 @@
         <x:v>strings</x:v>
       </x:c>
       <x:c r="K20" t="str">
-        <x:v>common-string-methods</x:v>
+        <x:v>split-and-join</x:v>
       </x:c>
       <x:c r="L20"/>
       <x:c r="M20" t="str">
-        <x:v>`mixed`</x:v>
+        <x:v>`text.split()` keeps all empty pieces between spaces.</x:v>
       </x:c>
       <x:c r="N20" t="str">
-        <x:v>`  mixed  `</x:v>
+        <x:v>`text.split()` produces `['red', 'blue']`, while `text.split(' ')` can produce empty pieces.</x:v>
       </x:c>
       <x:c r="O20" t="str">
-        <x:v>`  MiXeD  `</x:v>
+        <x:v>Both calls return the original string.</x:v>
       </x:c>
       <x:c r="P20" t="str">
-        <x:v>`MiXeD`</x:v>
+        <x:v>`text.split(' ')` removes the word `blue`.</x:v>
       </x:c>
       <x:c r="Q20" t="n">
-        <x:v>4</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A21" t="str">
         <x:v>Python - MCQ - 5.2.10</x:v>
       </x:c>
       <x:c r="B21" t="str">
-        <x:v>A date is stored as three string pieces:
-```python
-parts = ["2026", "07", "18"]
-print("/".join(parts))
+        <x:v>An email checker searches for a required at sign using a method that raises an error when the symbol is absent.
+```python
+email = "asha.example.com"
+position = email.index("@")
+status = "checked"
 ```
-What is printed?</x:v>
+What happens before `status` is assigned?</x:v>
       </x:c>
       <x:c r="C21" t="str">
-        <x:v>The separator is `/`, so `join` places it between the three string items and produces `2026/07/18`.</x:v>
+        <x:v>Unlike `find()`, `index()` does not return a sentinel for missing text; it raises an error.</x:v>
       </x:c>
       <x:c r="D21" t="n">
-        <x:v>5</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E21" t="str">
         <x:v>published</x:v>
       </x:c>
       <x:c r="F21" t="str">
-        <x:v>easy</x:v>
+        <x:v>hard</x:v>
       </x:c>
       <x:c r="G21" t="str">
-        <x:v>understand</x:v>
+        <x:v>analyze</x:v>
       </x:c>
       <x:c r="H21" t="str">
         <x:v>python - Set 2</x:v>
@@ -1558,51 +1504,50 @@
         <x:v>strings</x:v>
       </x:c>
       <x:c r="K21" t="str">
-        <x:v>splitting-and-joining</x:v>
+        <x:v>searching-and-membership</x:v>
       </x:c>
       <x:c r="L21"/>
       <x:c r="M21" t="str">
-        <x:v>`20260718`</x:v>
+        <x:v>`position` becomes `-1`.</x:v>
       </x:c>
       <x:c r="N21" t="str">
-        <x:v>`2026-07-18`</x:v>
+        <x:v>`position` becomes `0`.</x:v>
       </x:c>
       <x:c r="O21" t="str">
-        <x:v>`2026/07/18`</x:v>
+        <x:v>`position` becomes `None`.</x:v>
       </x:c>
       <x:c r="P21" t="str">
-        <x:v>`['2026', '07', '18']`</x:v>
+        <x:v>`index()` raises an error because `"@"` is absent.</x:v>
       </x:c>
       <x:c r="Q21" t="n">
-        <x:v>3</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" ht="79.19999694824219" hidden="0" customHeight="1">
       <x:c r="A22" t="str">
         <x:v>Python - MCQ - 5.2.11</x:v>
       </x:c>
       <x:c r="B22" t="str">
-        <x:v>A developer tries to join a code containing a number:
-```python
-parts = ["A", 2, "B"]
-print("-".join(parts))
-```
-What happens?</x:v>
+        <x:v>A campaign tracker counts a keyword written with several different capitalisations.
+```python
+text = "Sale sale SALE sale"
+matches = text.count("sale")
+```</x:v>
       </x:c>
       <x:c r="C22" t="str">
-        <x:v>`join` requires every item to already be a string. The integer 2 breaks that rule, so Python raises a `TypeError` instead of converting it automatically.</x:v>
+        <x:v>Searching is case-sensitive, so only the two lowercase occurrences match exactly.</x:v>
       </x:c>
       <x:c r="D22" t="n">
-        <x:v>8</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E22" t="str">
         <x:v>published</x:v>
       </x:c>
       <x:c r="F22" t="str">
-        <x:v>medium</x:v>
+        <x:v>easy</x:v>
       </x:c>
       <x:c r="G22" t="str">
-        <x:v>analyze</x:v>
+        <x:v>apply</x:v>
       </x:c>
       <x:c r="H22" t="str">
         <x:v>python - Set 2</x:v>
@@ -1614,40 +1559,35 @@
         <x:v>strings</x:v>
       </x:c>
       <x:c r="K22" t="str">
-        <x:v>splitting-and-joining</x:v>
+        <x:v>searching-and-membership</x:v>
       </x:c>
       <x:c r="L22"/>
       <x:c r="M22" t="str">
-        <x:v>It raises `TypeError` because 2 is not a string</x:v>
+        <x:v>`4`</x:v>
       </x:c>
       <x:c r="N22" t="str">
-        <x:v>It prints `A-2-B`</x:v>
+        <x:v>`3`</x:v>
       </x:c>
       <x:c r="O22" t="str">
-        <x:v>It prints `A-B` and skips 2</x:v>
+        <x:v>`2`</x:v>
       </x:c>
       <x:c r="P22" t="str">
-        <x:v>It raises `IndexError`</x:v>
+        <x:v>`1`</x:v>
       </x:c>
       <x:c r="Q22" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="23">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A23" t="str">
         <x:v>Python - MCQ - 5.2.12</x:v>
       </x:c>
       <x:c r="B23" t="str">
-        <x:v>A route is split into words and joined with a new separator:
-```python
-route = "north east west"
-steps = route.split()
-print("|".join(steps))
-```
-What is printed?</x:v>
+        <x:v>An order-import tool accepts files only when their names use a required prefix and CSV suffix.
+A file is accepted when its lowercase name begins with `"order_"` and ends with `".csv"`. Select the clearest check.</x:v>
       </x:c>
       <x:c r="C23" t="str">
-        <x:v>`split()` creates `['north', 'east', 'west']`. Joining those three pieces with `|` places the separator between them, producing `north|east|west`.</x:v>
+        <x:v>The two edge-specific methods directly express the prefix and suffix requirements after case normalisation.</x:v>
       </x:c>
       <x:c r="D23" t="n">
         <x:v>8</x:v>
@@ -1659,7 +1599,7 @@
         <x:v>medium</x:v>
       </x:c>
       <x:c r="G23" t="str">
-        <x:v>analyze</x:v>
+        <x:v>apply</x:v>
       </x:c>
       <x:c r="H23" t="str">
         <x:v>python - Set 2</x:v>
@@ -1671,51 +1611,50 @@
         <x:v>strings</x:v>
       </x:c>
       <x:c r="K23" t="str">
-        <x:v>splitting-and-joining</x:v>
+        <x:v>searching-and-membership</x:v>
       </x:c>
       <x:c r="L23"/>
       <x:c r="M23" t="str">
-        <x:v>`n|o|r|t|h`</x:v>
+        <x:v>`name.lower().startswith("order_") and name.lower().endswith(".csv")`</x:v>
       </x:c>
       <x:c r="N23" t="str">
-        <x:v>`north east west`</x:v>
+        <x:v>`"order_" in name or ".csv" in name`</x:v>
       </x:c>
       <x:c r="O23" t="str">
-        <x:v>`|north|east|west|`</x:v>
+        <x:v>`name.find("order_") and name.find(".csv")`</x:v>
       </x:c>
       <x:c r="P23" t="str">
-        <x:v>`north|east|west`</x:v>
+        <x:v>`name.count("order_.csv") == 2`</x:v>
       </x:c>
       <x:c r="Q23" t="n">
-        <x:v>4</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="24">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A24" t="str">
         <x:v>Python - MCQ - 5.2.13</x:v>
       </x:c>
       <x:c r="B24" t="str">
-        <x:v>The word `sale` is absent from `"new stock"`. What pair of results comes from these two searches?
-```python
-text = "new stock"
-print("sale" in text)
-print(text.find("sale"))
-```</x:v>
+        <x:v>A progress dashboard stores completion as a proportion but must present it as a readable percentage.
+```python
+completion = 0.873
+```
+The report must show `87.3%`. Select the correct f-string.</x:v>
       </x:c>
       <x:c r="C24" t="str">
-        <x:v>The `in` operator returns the boolean False when the text is absent. `find()` returns the special position -1 for the same missing text.</x:v>
+        <x:v>`.1%` multiplies the proportion by 100, uses one decimal place, and appends the percent sign.</x:v>
       </x:c>
       <x:c r="D24" t="n">
-        <x:v>8</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E24" t="str">
         <x:v>published</x:v>
       </x:c>
       <x:c r="F24" t="str">
-        <x:v>medium</x:v>
+        <x:v>hard</x:v>
       </x:c>
       <x:c r="G24" t="str">
-        <x:v>understand</x:v>
+        <x:v>apply</x:v>
       </x:c>
       <x:c r="H24" t="str">
         <x:v>python - Set 2</x:v>
@@ -1727,51 +1666,50 @@
         <x:v>strings</x:v>
       </x:c>
       <x:c r="K24" t="str">
-        <x:v>searching-within-strings</x:v>
+        <x:v>string-formatting</x:v>
       </x:c>
       <x:c r="L24"/>
       <x:c r="M24" t="str">
-        <x:v>`False` then `0`</x:v>
+        <x:v>`f"{completion:.1f}%"`</x:v>
       </x:c>
       <x:c r="N24" t="str">
-        <x:v>`False` then `-1`</x:v>
+        <x:v>`f"{completion:1%}"`</x:v>
       </x:c>
       <x:c r="O24" t="str">
-        <x:v>`-1` then `False`</x:v>
+        <x:v>`f"{completion * 100:.1f}"`</x:v>
       </x:c>
       <x:c r="P24" t="str">
-        <x:v>Both lines raise an error</x:v>
+        <x:v>`f"{completion:.1%}"`</x:v>
       </x:c>
       <x:c r="Q24" t="n">
-        <x:v>2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="25">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" ht="79.19999694824219" hidden="0" customHeight="1">
       <x:c r="A25" t="str">
         <x:v>Python - MCQ - 5.2.14</x:v>
       </x:c>
       <x:c r="B25" t="str">
-        <x:v>A fruit label is normalised before counting:
-```python
-fruit = "Banana"
-print(fruit.lower().count("a"))
-```
-What count is printed?</x:v>
+        <x:v>A shop price list aligns item names into a fixed-width left-hand column.
+```python
+item = "Clay"
+column = f"{item:_____}"
+```</x:v>
       </x:c>
       <x:c r="C25" t="str">
-        <x:v>Lower-casing produces `"banana"`. That text contains `a` at three positions, so `count("a")` returns 3.</x:v>
+        <x:v>`&lt;10` left-aligns the text in a field with minimum width ten.</x:v>
       </x:c>
       <x:c r="D25" t="n">
-        <x:v>8</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E25" t="str">
         <x:v>published</x:v>
       </x:c>
       <x:c r="F25" t="str">
-        <x:v>medium</x:v>
+        <x:v>easy</x:v>
       </x:c>
       <x:c r="G25" t="str">
-        <x:v>analyze</x:v>
+        <x:v>understand</x:v>
       </x:c>
       <x:c r="H25" t="str">
         <x:v>python - Set 2</x:v>
@@ -1783,39 +1721,35 @@
         <x:v>strings</x:v>
       </x:c>
       <x:c r="K25" t="str">
-        <x:v>searching-within-strings</x:v>
+        <x:v>string-formatting</x:v>
       </x:c>
       <x:c r="L25"/>
       <x:c r="M25" t="str">
+        <x:v>`&gt;10`</x:v>
+      </x:c>
+      <x:c r="N25" t="str">
+        <x:v>`&lt;10`</x:v>
+      </x:c>
+      <x:c r="O25" t="str">
+        <x:v>`^2`</x:v>
+      </x:c>
+      <x:c r="P25" t="str">
+        <x:v>`.10f`</x:v>
+      </x:c>
+      <x:c r="Q25" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="N25" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O25" t="str">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="P25" t="str">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="Q25" t="n">
-        <x:v>3</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="26">
+    </x:row>
+    <x:row r="26" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A26" t="str">
         <x:v>Python - MCQ - 5.2.15</x:v>
       </x:c>
       <x:c r="B26" t="str">
-        <x:v>A file filter should accept PDF extensions regardless of capitalisation:
-```python
-filename = "report.PDF"
-print(filename.lower().endswith(".pdf"))
-```
-What is printed?</x:v>
+        <x:v>A configuration tool stores a Windows-style path whose backslashes must remain literal characters.
+The path must retain the characters in `C:\new\table` rather than interpret `\n` and `\t`.</x:v>
       </x:c>
       <x:c r="C26" t="str">
-        <x:v>`filename.lower()` becomes `"report.pdf"`, which does end with `".pdf"`. The check therefore prints True.</x:v>
+        <x:v>The raw-string prefix tells Python to treat backslashes literally.</x:v>
       </x:c>
       <x:c r="D26" t="n">
         <x:v>8</x:v>
@@ -1827,7 +1761,7 @@
         <x:v>medium</x:v>
       </x:c>
       <x:c r="G26" t="str">
-        <x:v>apply</x:v>
+        <x:v>evaluate</x:v>
       </x:c>
       <x:c r="H26" t="str">
         <x:v>python - Set 2</x:v>
@@ -1839,34 +1773,35 @@
         <x:v>strings</x:v>
       </x:c>
       <x:c r="K26" t="str">
-        <x:v>searching-within-strings</x:v>
+        <x:v>escape-sequences</x:v>
       </x:c>
       <x:c r="L26"/>
       <x:c r="M26" t="str">
-        <x:v>False, because the original extension is uppercase</x:v>
+        <x:v>`path = r"C:\new\table"`</x:v>
       </x:c>
       <x:c r="N26" t="str">
-        <x:v>`.pdf`</x:v>
+        <x:v>`path = "C:\new\table"`</x:v>
       </x:c>
       <x:c r="O26" t="str">
-        <x:v>True</x:v>
+        <x:v>`path = f"C:\new\table"`</x:v>
       </x:c>
       <x:c r="P26" t="str">
-        <x:v>-1</x:v>
+        <x:v>`path = "C:/n/t"`</x:v>
       </x:c>
       <x:c r="Q26" t="n">
-        <x:v>3</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="27">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A27" t="str">
         <x:v>Python - MCQ - 5.2.16</x:v>
       </x:c>
       <x:c r="B27" t="str">
-        <x:v>A simple email check requires both an `@` somewhere in the text and a `.com` ending. Which condition expresses that rule?</x:v>
+        <x:v>A policy notice spans several lines and should remain readable in the Python source.
+A four-line notice must remain readable in the source and preserve its typed line breaks. Choose the most appropriate representation.</x:v>
       </x:c>
       <x:c r="C27" t="str">
-        <x:v>Both requirements must hold, so the condition joins the containment check and the ending check with `and`: `"@" in email and email.endswith(".com")`.</x:v>
+        <x:v>Triple quotes naturally preserve multiple physical lines and blank lines.</x:v>
       </x:c>
       <x:c r="D27" t="n">
         <x:v>8</x:v>
@@ -1878,7 +1813,7 @@
         <x:v>medium</x:v>
       </x:c>
       <x:c r="G27" t="str">
-        <x:v>apply</x:v>
+        <x:v>evaluate</x:v>
       </x:c>
       <x:c r="H27" t="str">
         <x:v>python - Set 2</x:v>
@@ -1890,39 +1825,35 @@
         <x:v>strings</x:v>
       </x:c>
       <x:c r="K27" t="str">
-        <x:v>searching-within-strings</x:v>
+        <x:v>escape-sequences</x:v>
       </x:c>
       <x:c r="L27"/>
       <x:c r="M27" t="str">
-        <x:v>`"@" in email and email.endswith(".com")`</x:v>
+        <x:v>Four unrelated variables with one word each</x:v>
       </x:c>
       <x:c r="N27" t="str">
-        <x:v>`"@" in email or email.endswith(".com")`</x:v>
+        <x:v>A standard quoted string broken across physical lines without escapes</x:v>
       </x:c>
       <x:c r="O27" t="str">
-        <x:v>`email.startswith("@") and ".com" in email`</x:v>
+        <x:v>A triple-quoted string containing the four lines</x:v>
       </x:c>
       <x:c r="P27" t="str">
-        <x:v>`email.find("@") == -1 and email.endswith(".com")`</x:v>
+        <x:v>An integer converted to text</x:v>
       </x:c>
       <x:c r="Q27" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="28">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A28" t="str">
         <x:v>Python - MCQ - 5.2.17</x:v>
       </x:c>
       <x:c r="B28" t="str">
-        <x:v>A receipt must always show two decimal places:
-```python
-amount = 7
-print(f"{amount:.2f}")
-```
-What appears?</x:v>
+        <x:v>A customer testimonial includes quotation marks that must appear inside a double-quoted literal.
+The outer delimiter must remain double quotes. Select the valid string for `She said "yes"`.</x:v>
       </x:c>
       <x:c r="C28" t="str">
-        <x:v>The `.2f` specifier displays the numeric value with exactly two digits after the decimal point, so 7 is shown as `7.00`.</x:v>
+        <x:v>Backslash-escaped double quotes are treated as content instead of delimiters.</x:v>
       </x:c>
       <x:c r="D28" t="n">
         <x:v>5</x:v>
@@ -1934,7 +1865,7 @@
         <x:v>easy</x:v>
       </x:c>
       <x:c r="G28" t="str">
-        <x:v>apply</x:v>
+        <x:v>analyze</x:v>
       </x:c>
       <x:c r="H28" t="str">
         <x:v>python - Set 2</x:v>
@@ -1946,50 +1877,51 @@
         <x:v>strings</x:v>
       </x:c>
       <x:c r="K28" t="str">
-        <x:v>string-formatting-and-fstrings</x:v>
+        <x:v>escape-sequences</x:v>
       </x:c>
       <x:c r="L28"/>
       <x:c r="M28" t="str">
-        <x:v>`7`</x:v>
+        <x:v>`text = "She said "yes""`</x:v>
       </x:c>
       <x:c r="N28" t="str">
-        <x:v>`7.2`</x:v>
+        <x:v>`text = "She said \"yes\""`</x:v>
       </x:c>
       <x:c r="O28" t="str">
-        <x:v>`7.0`</x:v>
+        <x:v>`text = She said "yes"`</x:v>
       </x:c>
       <x:c r="P28" t="str">
-        <x:v>`7.00`</x:v>
+        <x:v>`text = "She said /"yes/""`</x:v>
       </x:c>
       <x:c r="Q28" t="n">
-        <x:v>4</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="29">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A29" t="str">
         <x:v>Python - MCQ - 5.2.18</x:v>
       </x:c>
       <x:c r="B29" t="str">
-        <x:v>A status label uses this f-string field:
-```python
-print(f"{'OK':^6}")
+        <x:v>A social-media caption contains both a line break and an embedded quoted phrase.
+```python
+caption = "New
+"Craft" collection"
 ```
-What does `^6` request?</x:v>
+The intended value contains a newline followed by `"Craft" collection`. Approve the complete one-line repair.</x:v>
       </x:c>
       <x:c r="C29" t="str">
-        <x:v>The width is 6 and `^` means centre alignment. Python places `OK` in the middle of a six-character field, padding both sides with spaces.</x:v>
+        <x:v>The physical newline becomes `\n`, and both embedded double quotes are escaped.</x:v>
       </x:c>
       <x:c r="D29" t="n">
-        <x:v>8</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E29" t="str">
         <x:v>published</x:v>
       </x:c>
       <x:c r="F29" t="str">
-        <x:v>medium</x:v>
+        <x:v>hard</x:v>
       </x:c>
       <x:c r="G29" t="str">
-        <x:v>understand</x:v>
+        <x:v>evaluate</x:v>
       </x:c>
       <x:c r="H29" t="str">
         <x:v>python - Set 2</x:v>
@@ -2001,46 +1933,51 @@
         <x:v>strings</x:v>
       </x:c>
       <x:c r="K29" t="str">
-        <x:v>string-formatting-and-fstrings</x:v>
+        <x:v>escape-sequences</x:v>
       </x:c>
       <x:c r="L29"/>
       <x:c r="M29" t="str">
-        <x:v>Right-align `OK` in a field of width 6</x:v>
+        <x:v>`caption = "New/nCraft collection"`</x:v>
       </x:c>
       <x:c r="N29" t="str">
-        <x:v>Centre `OK` in a field of width 6</x:v>
+        <x:v>`caption = "New"\n"Craft collection"`</x:v>
       </x:c>
       <x:c r="O29" t="str">
-        <x:v>Repeat `OK` six times</x:v>
+        <x:v>`caption = 'New\n'Craft' collection'`</x:v>
       </x:c>
       <x:c r="P29" t="str">
-        <x:v>Show six decimal places</x:v>
+        <x:v>`caption = "New\n\"Craft\" collection"`</x:v>
       </x:c>
       <x:c r="Q29" t="n">
-        <x:v>2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="30">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A30" t="str">
         <x:v>Python - MCQ - 5.2.19</x:v>
       </x:c>
       <x:c r="B30" t="str">
-        <x:v>A team is choosing the modern recommended style for inserting `name` and `age` into a sentence. Which line uses an f-string?</x:v>
+        <x:v>A giveaway organiser cleans punctuation and capitalisation before counting the words in an entry.
+```python
+raw = "  Python, python, CRAFT  "
+clean = raw.strip().lower().replace(",", "")
+word_count = len(clean.split())
+```</x:v>
       </x:c>
       <x:c r="C30" t="str">
-        <x:v>An f-string has the `f` prefix and places expressions directly inside braces. `f"{name} is {age}"` is the modern, readable form introduced in the lesson.</x:v>
+        <x:v>Cleaning produces `"python python craft"`, which splits into three words.</x:v>
       </x:c>
       <x:c r="D30" t="n">
-        <x:v>5</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="E30" t="str">
         <x:v>published</x:v>
       </x:c>
       <x:c r="F30" t="str">
-        <x:v>easy</x:v>
+        <x:v>medium</x:v>
       </x:c>
       <x:c r="G30" t="str">
-        <x:v>understand</x:v>
+        <x:v>evaluate</x:v>
       </x:c>
       <x:c r="H30" t="str">
         <x:v>python - Set 2</x:v>
@@ -2052,38 +1989,39 @@
         <x:v>strings</x:v>
       </x:c>
       <x:c r="K30" t="str">
-        <x:v>string-formatting-and-fstrings</x:v>
+        <x:v>text-processing</x:v>
       </x:c>
       <x:c r="L30"/>
       <x:c r="M30" t="str">
-        <x:v>`f"{name} is {age}"`</x:v>
+        <x:v>`2`</x:v>
       </x:c>
       <x:c r="N30" t="str">
-        <x:v>`"{} is {}".format(name, age)`</x:v>
+        <x:v>`4`</x:v>
       </x:c>
       <x:c r="O30" t="str">
-        <x:v>`"%s is %d" % (name, age)`</x:v>
+        <x:v>`3`</x:v>
       </x:c>
       <x:c r="P30" t="str">
-        <x:v>`name + " is " + age`</x:v>
+        <x:v>`22`</x:v>
       </x:c>
       <x:c r="Q30" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="31">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A31" t="str">
         <x:v>Python - MCQ - 5.2.20</x:v>
       </x:c>
       <x:c r="B31" t="str">
-        <x:v>A path label needs one visible backslash:
-```python
-print("C:\\temp")
+        <x:v>A structured-entry importer expects three comma-separated fields but receives only two.
+```python
+line = "Asha,19"
+name, age, city = line.split(",")
 ```
-What appears?</x:v>
+Select the correct review finding.</x:v>
       </x:c>
       <x:c r="C31" t="str">
-        <x:v>Inside a normal string, `\\` represents one literal backslash. The printed text is therefore `C:\temp`.</x:v>
+        <x:v>The number of produced pieces must match the number of target variables during unpacking.</x:v>
       </x:c>
       <x:c r="D31" t="n">
         <x:v>8</x:v>
@@ -2095,7 +2033,7 @@
         <x:v>medium</x:v>
       </x:c>
       <x:c r="G31" t="str">
-        <x:v>analyze</x:v>
+        <x:v>evaluate</x:v>
       </x:c>
       <x:c r="H31" t="str">
         <x:v>python - Set 2</x:v>
@@ -2107,34 +2045,38 @@
         <x:v>strings</x:v>
       </x:c>
       <x:c r="K31" t="str">
-        <x:v>escape-sequences-and-multiline-strings</x:v>
+        <x:v>text-processing</x:v>
       </x:c>
       <x:c r="L31"/>
       <x:c r="M31" t="str">
-        <x:v>`C:temp`</x:v>
+        <x:v>Splitting returns two pieces, so unpacking into three variables raises an error.</x:v>
       </x:c>
       <x:c r="N31" t="str">
-        <x:v>`C:` followed by a tab and `emp`</x:v>
+        <x:v>`city` automatically becomes an empty string.</x:v>
       </x:c>
       <x:c r="O31" t="str">
-        <x:v>`C:\\temp` with two visible backslashes</x:v>
+        <x:v>`age` and `city` both become `"19"`.</x:v>
       </x:c>
       <x:c r="P31" t="str">
-        <x:v>`C:\temp` with one visible backslash</x:v>
+        <x:v>`split()` refuses comma separators.</x:v>
       </x:c>
       <x:c r="Q31" t="n">
-        <x:v>4</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="32">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" ht="79.19999694824219" hidden="0" customHeight="1">
       <x:c r="A32" t="str">
         <x:v>Python - MCQ - 5.2.21</x:v>
       </x:c>
       <x:c r="B32" t="str">
-        <x:v>A welcome email contains several lines and a blank line that must be kept exactly as typed. Which string form is most suitable?</x:v>
+        <x:v>A content dashboard reports character count after excluding ordinary spaces.
+```python
+sentence = "red clay art"
+characters_without_spaces = __________
+```</x:v>
       </x:c>
       <x:c r="C32" t="str">
-        <x:v>A triple-quoted string preserves the line breaks and blank lines written between its opening and closing quotes, making it the clearest choice for a multi-line message.</x:v>
+        <x:v>Removing spaces creates the text to be measured; `len()` then counts its remaining characters.</x:v>
       </x:c>
       <x:c r="D32" t="n">
         <x:v>8</x:v>
@@ -2146,7 +2088,7 @@
         <x:v>medium</x:v>
       </x:c>
       <x:c r="G32" t="str">
-        <x:v>understand</x:v>
+        <x:v>analyze</x:v>
       </x:c>
       <x:c r="H32" t="str">
         <x:v>python - Set 2</x:v>
@@ -2158,52 +2100,54 @@
         <x:v>strings</x:v>
       </x:c>
       <x:c r="K32" t="str">
-        <x:v>escape-sequences-and-multiline-strings</x:v>
+        <x:v>text-processing</x:v>
       </x:c>
       <x:c r="L32"/>
       <x:c r="M32" t="str">
-        <x:v>A single-quoted string with the line breaks removed</x:v>
+        <x:v>`sentence.count(" ")`</x:v>
       </x:c>
       <x:c r="N32" t="str">
-        <x:v>A raw string on one line</x:v>
+        <x:v>`len(sentence.replace(" ", ""))`</x:v>
       </x:c>
       <x:c r="O32" t="str">
-        <x:v>A triple-quoted string</x:v>
+        <x:v>`len(sentence.split(" "))`</x:v>
       </x:c>
       <x:c r="P32" t="str">
-        <x:v>A string processed with `.split()`</x:v>
+        <x:v>`sentence.find(" ")`</x:v>
       </x:c>
       <x:c r="Q32" t="n">
-        <x:v>3</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="33">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" ht="171.60000610351562" hidden="0" customHeight="1">
       <x:c r="A33" t="str">
         <x:v>Python - MCQ - 5.2.22</x:v>
       </x:c>
       <x:c r="B33" t="str">
-        <x:v>A normal string and a raw string contain the same two typed symbols:
-```python
-normal = "\n"
-raw = r"\n"
-print(len(normal), len(raw))
+        <x:v>A cleanup team is checking whether trimming before replacement behaves the same as replacing before trimming.
+For `text = "  tea  "`, compare:
+```python
+# Version A
+text.strip().replace(" ", "-")
+# Version B
+text.replace(" ", "-").strip()
 ```
-What is printed?</x:v>
+Select the accurate result pair.</x:v>
       </x:c>
       <x:c r="C33" t="str">
-        <x:v>In the normal string, `\n` becomes one newline character, so its length is 1. In the raw string, the backslash and `n` stay as two separate characters, so its length is 2.</x:v>
+        <x:v>Version A removes edge spaces before replacement; Version B turns them into hyphens, which `strip()` does not remove.</x:v>
       </x:c>
       <x:c r="D33" t="n">
-        <x:v>8</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E33" t="str">
         <x:v>published</x:v>
       </x:c>
       <x:c r="F33" t="str">
-        <x:v>medium</x:v>
+        <x:v>hard</x:v>
       </x:c>
       <x:c r="G33" t="str">
-        <x:v>analyze</x:v>
+        <x:v>evaluate</x:v>
       </x:c>
       <x:c r="H33" t="str">
         <x:v>python - Set 2</x:v>
@@ -2215,52 +2159,50 @@
         <x:v>strings</x:v>
       </x:c>
       <x:c r="K33" t="str">
-        <x:v>escape-sequences-and-multiline-strings</x:v>
+        <x:v>string-methods</x:v>
       </x:c>
       <x:c r="L33"/>
       <x:c r="M33" t="str">
-        <x:v>`2 2`</x:v>
+        <x:v>Both produce `"tea"`.</x:v>
       </x:c>
       <x:c r="N33" t="str">
-        <x:v>`1 2`</x:v>
+        <x:v>A produces `"--tea--"`; B produces `"tea"`.</x:v>
       </x:c>
       <x:c r="O33" t="str">
-        <x:v>`1 1`</x:v>
+        <x:v>Both produce `"--tea--"`.</x:v>
       </x:c>
       <x:c r="P33" t="str">
-        <x:v>`2 1`</x:v>
+        <x:v>A produces `"tea"`; B produces `"--tea--"`.</x:v>
       </x:c>
       <x:c r="Q33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="34">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" ht="79.19999694824219" hidden="0" customHeight="1">
       <x:c r="A34" t="str">
         <x:v>Python - MCQ - 5.2.23</x:v>
       </x:c>
       <x:c r="B34" t="str">
-        <x:v>A text analyser cleans a short phrase and reports two measures:
-```python
-clean = "  red blue  ".strip()
-print(len(clean.split()))
-print(len(clean.replace(" ", "")))
-```
-What are the two results?</x:v>
+        <x:v>A content-moderation search must find a keyword regardless of how users capitalise it.
+```python
+sentence = "Learn PYTHON Today"
+contains_python = __________
+```</x:v>
       </x:c>
       <x:c r="C34" t="str">
-        <x:v>The cleaned text is `"red blue"`. Splitting produces two words, while removing its one space leaves `"redblue"`, which has 7 characters. The program prints 2, then 7.</x:v>
+        <x:v>Lowercasing the searchable text makes membership independent of the original capitalisation.</x:v>
       </x:c>
       <x:c r="D34" t="n">
-        <x:v>8</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E34" t="str">
         <x:v>published</x:v>
       </x:c>
       <x:c r="F34" t="str">
-        <x:v>medium</x:v>
+        <x:v>easy</x:v>
       </x:c>
       <x:c r="G34" t="str">
-        <x:v>analyze</x:v>
+        <x:v>understand</x:v>
       </x:c>
       <x:c r="H34" t="str">
         <x:v>python - Set 2</x:v>
@@ -2272,49 +2214,51 @@
         <x:v>strings</x:v>
       </x:c>
       <x:c r="K34" t="str">
-        <x:v>practical-text-processing</x:v>
+        <x:v>searching-and-membership</x:v>
       </x:c>
       <x:c r="L34"/>
       <x:c r="M34" t="str">
-        <x:v>2 then 8</x:v>
+        <x:v>`"python" in sentence.lower()`</x:v>
       </x:c>
       <x:c r="N34" t="str">
-        <x:v>1 then 7</x:v>
+        <x:v>`"python" == sentence`</x:v>
       </x:c>
       <x:c r="O34" t="str">
-        <x:v>2 then 6</x:v>
+        <x:v>`sentence.find("PYTHON") == -1`</x:v>
       </x:c>
       <x:c r="P34" t="str">
-        <x:v>2 then 7</x:v>
+        <x:v>`sentence.count("python") == 0`</x:v>
       </x:c>
       <x:c r="Q34" t="n">
-        <x:v>4</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="35">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" ht="158.39999389648438" hidden="0" customHeight="1">
       <x:c r="A35" t="str">
         <x:v>Python - MCQ - 5.2.24</x:v>
       </x:c>
       <x:c r="B35" t="str">
-        <x:v>A CSV-style record is split and unpacked:
-```python
-record = "Asha,20,Pune"
-name, age, city = record.split(",")
-print(city)
+        <x:v>A keyword appears at the very beginning of a caption, but the search condition mistakenly reports failure.
+```python
+text = "craft sale"
+if text.find("craft"):
+    status = "Found"
+else:
+    status = "Missing"
 ```
-What is printed?</x:v>
+The word exists at the beginning. Why is `status` still `"Missing"`?</x:v>
       </x:c>
       <x:c r="C35" t="str">
-        <x:v>The three pieces are assigned in order: `Asha` to `name`, `20` to `age`, and `Pune` to `city`. Printing `city` therefore shows `Pune`.</x:v>
+        <x:v>Zero is a valid position but a falsy condition value, so the sentinel must be tested explicitly.</x:v>
       </x:c>
       <x:c r="D35" t="n">
-        <x:v>5</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="E35" t="str">
         <x:v>published</x:v>
       </x:c>
       <x:c r="F35" t="str">
-        <x:v>easy</x:v>
+        <x:v>medium</x:v>
       </x:c>
       <x:c r="G35" t="str">
         <x:v>analyze</x:v>
@@ -2329,42 +2273,40 @@
         <x:v>strings</x:v>
       </x:c>
       <x:c r="K35" t="str">
-        <x:v>practical-text-processing</x:v>
+        <x:v>searching-and-membership</x:v>
       </x:c>
       <x:c r="L35"/>
       <x:c r="M35" t="str">
-        <x:v>`Pune`</x:v>
+        <x:v>`find()` is case-insensitive.</x:v>
       </x:c>
       <x:c r="N35" t="str">
-        <x:v>`20`</x:v>
+        <x:v>`find()` returns `-1` for a match.</x:v>
       </x:c>
       <x:c r="O35" t="str">
-        <x:v>`Asha`</x:v>
+        <x:v>`find()` returns index `0`, which is falsy; compare the result with `-1` instead.</x:v>
       </x:c>
       <x:c r="P35" t="str">
-        <x:v>The entire record</x:v>
+        <x:v>`find()` works only on one-character searches.</x:v>
       </x:c>
       <x:c r="Q35" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="36">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" ht="132" hidden="0" customHeight="1">
       <x:c r="A36" t="str">
         <x:v>Python - MCQ - 5.2.25</x:v>
       </x:c>
       <x:c r="B36" t="str">
-        <x:v>An age field accepts whole-number digits but users sometimes type outer spaces:
-```python
-entry = input("Age: ")
-if entry.isdigit():
-    print("Accepted")
-else:
-    print("Digits only")
+        <x:v>A message checker inspects the final character even when the user may submit an empty string.
+```python
+text = input("Text: ")
+if text[-1] == ".":
+    status = "Sentence"
 ```
-Which input is rejected now but would pass after changing the check to `entry.strip().isdigit()`?</x:v>
+What is the smallest safe structural repair?</x:v>
       </x:c>
       <x:c r="C36" t="str">
-        <x:v>`" 25 "` contains spaces, so its direct `isdigit()` result is False. After `strip()`, it becomes `"25"`, whose characters are all digits. The other invalid choices still contain non-digits or no characters.</x:v>
+        <x:v>Empty input has no last character; a truthiness guard prevents out-of-range indexing.</x:v>
       </x:c>
       <x:c r="D36" t="n">
         <x:v>8</x:v>
@@ -2388,46 +2330,47 @@
         <x:v>strings</x:v>
       </x:c>
       <x:c r="K36" t="str">
-        <x:v>common-string-methods</x:v>
+        <x:v>indexing-and-slicing</x:v>
       </x:c>
       <x:c r="L36"/>
       <x:c r="M36" t="str">
-        <x:v>`25`</x:v>
+        <x:v>Use `text[0]` instead.</x:v>
       </x:c>
       <x:c r="N36" t="str">
-        <x:v>`2a`</x:v>
+        <x:v>Replace `-1` with `1`.</x:v>
       </x:c>
       <x:c r="O36" t="str">
-        <x:v>` 25 `</x:v>
+        <x:v>Convert `text` to an integer first.</x:v>
       </x:c>
       <x:c r="P36" t="str">
-        <x:v>An empty string</x:v>
+        <x:v>Check that `text` is non-empty before evaluating `text[-1]`.</x:v>
       </x:c>
       <x:c r="Q36" t="n">
-        <x:v>3</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="37">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A37" t="str">
         <x:v>Python - MCQ - 5.2.26</x:v>
       </x:c>
       <x:c r="B37" t="str">
-        <x:v>A caption counter must count every character except spaces, while keeping punctuation. Which expression fits?</x:v>
+        <x:v>A product preview should return up to five characters without failing on shorter names.
+A preview should return up to the first five characters, even when the source contains fewer than five. Choose the safest expression.</x:v>
       </x:c>
       <x:c r="C37" t="str">
-        <x:v>Replacing spaces with the empty string removes only spaces. Measuring the result with `len()` still counts letters and punctuation: `len(text.replace(" ", ""))`.</x:v>
+        <x:v>Slicing safely returns the available prefix without requiring five characters to exist.</x:v>
       </x:c>
       <x:c r="D37" t="n">
-        <x:v>8</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E37" t="str">
         <x:v>published</x:v>
       </x:c>
       <x:c r="F37" t="str">
-        <x:v>medium</x:v>
+        <x:v>easy</x:v>
       </x:c>
       <x:c r="G37" t="str">
-        <x:v>apply</x:v>
+        <x:v>evaluate</x:v>
       </x:c>
       <x:c r="H37" t="str">
         <x:v>python - Set 2</x:v>
@@ -2439,54 +2382,52 @@
         <x:v>strings</x:v>
       </x:c>
       <x:c r="K37" t="str">
-        <x:v>practical-text-processing</x:v>
+        <x:v>indexing-and-slicing</x:v>
       </x:c>
       <x:c r="L37"/>
       <x:c r="M37" t="str">
-        <x:v>`len(text.split())`</x:v>
+        <x:v>`text[5]`</x:v>
       </x:c>
       <x:c r="N37" t="str">
-        <x:v>`len(text.replace(" ", ""))`</x:v>
+        <x:v>`text[:5]`</x:v>
       </x:c>
       <x:c r="O37" t="str">
-        <x:v>`text.count(" ")`</x:v>
+        <x:v>`text[-5]`</x:v>
       </x:c>
       <x:c r="P37" t="str">
-        <x:v>`len(text.strip())`</x:v>
+        <x:v>`text[0] + text[1] + text[2] + text[3] + text[4]`</x:v>
       </x:c>
       <x:c r="Q37" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
-    <x:row r="38">
+    <x:row r="38" ht="132" hidden="0" customHeight="1">
       <x:c r="A38" t="str">
         <x:v>Python - MCQ - 5.2.27</x:v>
       </x:c>
       <x:c r="B38" t="str">
-        <x:v>Two versions try to capitalise `name = "asha"`:
-```python
-# Version A
-result_a = name[0].upper() + name[1:]
-# Version B
-result_b = name
-result_b.capitalize()
+        <x:v>A marketing tool converts a multi-word craft phrase into one title-cased hashtag with no spaces.
+```python
+phrase = "handmade clay art"
+words = phrase.title().split()
+hashtag = "#" + __________
 ```
-What values do the two result variables hold?</x:v>
+The required result is `#HandmadeClayArt`.</x:v>
       </x:c>
       <x:c r="C38" t="str">
-        <x:v>Version A builds and stores the new string `"Asha"`. Version B calls `capitalize()` but discards its returned string, so `result_b` stays `"asha"`. Neither version edits the original string in place.</x:v>
+        <x:v>Joining with the empty string fuses the transformed words without separators.</x:v>
       </x:c>
       <x:c r="D38" t="n">
-        <x:v>10</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="E38" t="str">
         <x:v>published</x:v>
       </x:c>
       <x:c r="F38" t="str">
-        <x:v>hard</x:v>
+        <x:v>medium</x:v>
       </x:c>
       <x:c r="G38" t="str">
-        <x:v>analyze</x:v>
+        <x:v>apply</x:v>
       </x:c>
       <x:c r="H38" t="str">
         <x:v>python - Set 2</x:v>
@@ -2498,34 +2439,39 @@
         <x:v>strings</x:v>
       </x:c>
       <x:c r="K38" t="str">
-        <x:v>string-immutability</x:v>
+        <x:v>split-and-join</x:v>
       </x:c>
       <x:c r="L38"/>
       <x:c r="M38" t="str">
-        <x:v>Both hold `Asha`</x:v>
+        <x:v>`" ".join(words)`</x:v>
       </x:c>
       <x:c r="N38" t="str">
-        <x:v>Both hold `asha`</x:v>
+        <x:v>`",".join(words)`</x:v>
       </x:c>
       <x:c r="O38" t="str">
-        <x:v>Version A holds `asha`; Version B holds `Asha`</x:v>
+        <x:v>`"".join(words)`</x:v>
       </x:c>
       <x:c r="P38" t="str">
-        <x:v>Version A holds `Asha`; Version B holds `asha`</x:v>
+        <x:v>`words.split()`</x:v>
       </x:c>
       <x:c r="Q38" t="n">
-        <x:v>4</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="39">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A39" t="str">
         <x:v>Python - MCQ - 5.2.28</x:v>
       </x:c>
       <x:c r="B39" t="str">
-        <x:v>A log code is `CODING`, and a report needs the middle text `DIN`. Which slice produces it?</x:v>
+        <x:v>A user-profile service stores both the original display name and a separate uppercase version.
+```python
+original = "Meera"
+upper_name = original.upper()
+```
+Complete the final state pair.</x:v>
       </x:c>
       <x:c r="C39" t="str">
-        <x:v>In `CODING`, indexes 2, 3, and 4 are `D`, `I`, and `N`. A stop of 5 excludes index 5, so `code[2:5]` returns `DIN`.</x:v>
+        <x:v>The method returns a new uppercase string while leaving the original immutable value unchanged.</x:v>
       </x:c>
       <x:c r="D39" t="n">
         <x:v>8</x:v>
@@ -2549,46 +2495,51 @@
         <x:v>strings</x:v>
       </x:c>
       <x:c r="K39" t="str">
-        <x:v>indexing-and-slicing</x:v>
+        <x:v>string-methods</x:v>
       </x:c>
       <x:c r="L39"/>
       <x:c r="M39" t="str">
-        <x:v>`code[1:4]`</x:v>
+        <x:v>`original == "Meera"`; `upper_name == "MEERA"`</x:v>
       </x:c>
       <x:c r="N39" t="str">
-        <x:v>`code[2:4]`</x:v>
+        <x:v>Both variables contain `"MEERA"`.</x:v>
       </x:c>
       <x:c r="O39" t="str">
-        <x:v>`code[2:5]`</x:v>
+        <x:v>Both variables contain `"Meera"`.</x:v>
       </x:c>
       <x:c r="P39" t="str">
-        <x:v>`code[3:6]`</x:v>
+        <x:v>`original` becomes empty after the method call.</x:v>
       </x:c>
       <x:c r="Q39" t="n">
-        <x:v>3</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="40">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A40" t="str">
         <x:v>Python - MCQ - 5.2.29</x:v>
       </x:c>
       <x:c r="B40" t="str">
-        <x:v>A notification must store the text `She said "ready"`. Which literal uses the safest quote style without escape codes?</x:v>
+        <x:v>A signup form uses only an at-sign check and a `.com` suffix as rough email validation.
+```python
+email = input("Email: ").strip().lower()
+valid = "@" in email and email.endswith(".com")
+```
+Which input proves that this is only a rough check rather than complete email validation?</x:v>
       </x:c>
       <x:c r="C40" t="str">
-        <x:v>The text contains double quotes but no apostrophe, so single quotes can wrap the whole string safely: `'She said "ready"'`. The inner double quotes then remain ordinary characters.</x:v>
+        <x:v>`"@.com"` satisfies both simple checks despite lacking meaningful text around the at sign.</x:v>
       </x:c>
       <x:c r="D40" t="n">
-        <x:v>8</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E40" t="str">
         <x:v>published</x:v>
       </x:c>
       <x:c r="F40" t="str">
-        <x:v>medium</x:v>
+        <x:v>hard</x:v>
       </x:c>
       <x:c r="G40" t="str">
-        <x:v>apply</x:v>
+        <x:v>analyze</x:v>
       </x:c>
       <x:c r="H40" t="str">
         <x:v>python - Set 2</x:v>
@@ -2600,41 +2551,35 @@
         <x:v>strings</x:v>
       </x:c>
       <x:c r="K40" t="str">
-        <x:v>what-is-a-string</x:v>
+        <x:v>text-processing</x:v>
       </x:c>
       <x:c r="L40"/>
       <x:c r="M40" t="str">
-        <x:v>`"She said "ready""`</x:v>
+        <x:v>`"asha@example.com"`</x:v>
       </x:c>
       <x:c r="N40" t="str">
-        <x:v>`'She said "ready"'`</x:v>
+        <x:v>`"  ASHA@EXAMPLE.COM  "`</x:v>
       </x:c>
       <x:c r="O40" t="str">
-        <x:v>`She said "ready"`</x:v>
+        <x:v>`"asha.example.com"`</x:v>
       </x:c>
       <x:c r="P40" t="str">
-        <x:v>`"She said ready"`</x:v>
+        <x:v>`"@.com"`</x:v>
       </x:c>
       <x:c r="Q40" t="n">
-        <x:v>2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="41">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A41" t="str">
         <x:v>Python - MCQ - 5.2.30</x:v>
       </x:c>
       <x:c r="B41" t="str">
-        <x:v>Two cleaning pipelines process `raw = "  A,B  "`:
-```python
-# Version A
-clean_a = raw.strip().replace(",", "").lower()
-# Version B
-clean_b = raw.replace(",", "").lower()
-```
-Are their results equivalent?</x:v>
+        <x:v>A content-analytics tool must clean text once, count words and non-space characters, and perform a case-insensitive search.
+A tool must trim input, normalise case, count words, count non-space characters, and perform a case-insensitive keyword check. Approve the control plan.</x:v>
       </x:c>
       <x:c r="C41" t="str">
-        <x:v>No. Version A removes the outer spaces before removing the comma and lower-casing, so it produces `"ab"`. Version B never strips the outer spaces, so it produces `"  ab  "`.</x:v>
+        <x:v>The pipeline cleans once, then applies the appropriate splitting, replacement, length, and membership tools to the normalised text.</x:v>
       </x:c>
       <x:c r="D41" t="n">
         <x:v>8</x:v>
@@ -2646,7 +2591,7 @@
         <x:v>medium</x:v>
       </x:c>
       <x:c r="G41" t="str">
-        <x:v>analyze</x:v>
+        <x:v>evaluate</x:v>
       </x:c>
       <x:c r="H41" t="str">
         <x:v>python - Set 2</x:v>
@@ -2658,23 +2603,23 @@
         <x:v>strings</x:v>
       </x:c>
       <x:c r="K41" t="str">
-        <x:v>practical-text-processing</x:v>
+        <x:v>text-processing</x:v>
       </x:c>
       <x:c r="L41"/>
       <x:c r="M41" t="str">
-        <x:v>No; Version A gives `ab`, while Version B keeps the outer spaces</x:v>
+        <x:v>Search the raw input first and never store cleaned text.</x:v>
       </x:c>
       <x:c r="N41" t="str">
-        <x:v>Yes; method order never affects text cleaning</x:v>
+        <x:v>Store `clean = raw.strip().lower()`, use `len(clean.split())`, use `len(clean.replace(" ", ""))`, and test the lowercased keyword with `in`.</x:v>
       </x:c>
       <x:c r="O41" t="str">
-        <x:v>No; Version A keeps the comma and Version B removes it</x:v>
+        <x:v>Convert the sentence to an integer and then split it.</x:v>
       </x:c>
       <x:c r="P41" t="str">
-        <x:v>Yes; both produce `A,B`</x:v>
+        <x:v>Use `index()` for every search and assume the keyword exists.</x:v>
       </x:c>
       <x:c r="Q41" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/content/Question Bank/MCQ/Python/Unit 5 - Strings/Unit 5 - Strings - MCQ.xlsx
+++ b/content/Question Bank/MCQ/Python/Unit 5 - Strings/Unit 5 - Strings - MCQ.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Python - MCQ - 5" sheetId="1" r:id="Rc0f30f7b4b7146ba"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Python - MCQ - 5" sheetId="1" r:id="R4aeb1a56a5b74c76"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -426,11 +426,11 @@
         <x:v>Python - MCQ - 5.1.1</x:v>
       </x:c>
       <x:c r="B2" t="str">
-        <x:v>A craft-shop owner is storing a brand name that contains an apostrophe and must not break the Python literal.
-The stored text must be exactly `Meera's Crafts`. Select the simplest valid literal.</x:v>
+        <x:v>A username counter includes the separator
+A craft-page username field contains `"Meera Arts"`. Its counter uses `len()` and treats every character, including spaces, as part of the text. Which count will appear beside the field?</x:v>
       </x:c>
       <x:c r="C2" t="str">
-        <x:v>Double quotes safely delimit text that contains an apostrophe.</x:v>
+        <x:v>The nine letters plus the space give a total length of 10.</x:v>
       </x:c>
       <x:c r="D2" t="n">
         <x:v>5</x:v>
@@ -442,7 +442,7 @@
         <x:v>easy</x:v>
       </x:c>
       <x:c r="G2" t="str">
-        <x:v>evaluate</x:v>
+        <x:v>apply</x:v>
       </x:c>
       <x:c r="H2" t="str">
         <x:v>python - Set 1</x:v>
@@ -458,16 +458,16 @@
       </x:c>
       <x:c r="L2"/>
       <x:c r="M2" t="str">
-        <x:v>`shop = 'Meera's Crafts'`</x:v>
+        <x:v>`9`</x:v>
       </x:c>
       <x:c r="N2" t="str">
-        <x:v>`shop = "Meera's Crafts"`</x:v>
+        <x:v>`10`</x:v>
       </x:c>
       <x:c r="O2" t="str">
-        <x:v>`shop = Meera's Crafts`</x:v>
+        <x:v>`11`</x:v>
       </x:c>
       <x:c r="P2" t="str">
-        <x:v>`shop = "Meera"s Crafts"`</x:v>
+        <x:v>`2`</x:v>
       </x:c>
       <x:c r="Q2" t="n">
         <x:v>2</x:v>
@@ -478,26 +478,25 @@
         <x:v>Python - MCQ - 5.1.2</x:v>
       </x:c>
       <x:c r="B3" t="str">
-        <x:v>A product-code parser reads the first and last characters of a five-letter code before requesting one additional position.
+        <x:v>Repairing an off-by-one category slice
+A product code stores its category at indices 2 through 5 inclusive. The current slice loses the final category character:
 ```python
-word = "Craft"
-first = word[0]
-last = word[-1]
-extra = word[5]
+code = "ABCD1234"
+category = code[2:5]       # currently "CD1"
 ```
-Record the outcome of the third assignment.</x:v>
+Which smallest replacement produces the required `"CD12"` without changing the starting index?</x:v>
       </x:c>
       <x:c r="C3" t="str">
-        <x:v>A five-character string has valid positive indices 0 through 4.</x:v>
+        <x:v>Slice stops are exclusive, so changing the stop from 5 to 6 includes index 5 and produces `"CD12"`.</x:v>
       </x:c>
       <x:c r="D3" t="n">
-        <x:v>8</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E3" t="str">
         <x:v>published</x:v>
       </x:c>
       <x:c r="F3" t="str">
-        <x:v>medium</x:v>
+        <x:v>easy</x:v>
       </x:c>
       <x:c r="G3" t="str">
         <x:v>analyze</x:v>
@@ -516,47 +515,49 @@
       </x:c>
       <x:c r="L3"/>
       <x:c r="M3" t="str">
-        <x:v>`extra` becomes `"t"`.</x:v>
+        <x:v>`code[2:5:2]`</x:v>
       </x:c>
       <x:c r="N3" t="str">
-        <x:v>`extra` becomes `""`.</x:v>
+        <x:v>`code[1:5]`</x:v>
       </x:c>
       <x:c r="O3" t="str">
-        <x:v>`extra` becomes `None`.</x:v>
+        <x:v>`code[2:7]`</x:v>
       </x:c>
       <x:c r="P3" t="str">
-        <x:v>Python raises `IndexError` because index 5 does not exist.</x:v>
+        <x:v>`code[2:6]`</x:v>
       </x:c>
       <x:c r="Q3" t="n">
         <x:v>4</x:v>
       </x:c>
     </x:row>
-    <x:row r="4" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="4" ht="145.1999969482422" hidden="0" customHeight="1">
       <x:c r="A4" t="str">
         <x:v>Python - MCQ - 5.1.3</x:v>
       </x:c>
       <x:c r="B4" t="str">
-        <x:v>A username was saved with the wrong first letter, and the developer must correct it without editing a string in place.
+        <x:v>Retaining a cleaned required name
+A registration field containing only spaces must become an empty string after cleaning, and its validity flag must then be false:
 ```python
-username = "neera"
-username[0] = "m"
+name = "   "
+name.strip()
+has_name = bool(name)
 ```
-Approve the smallest repair that creates `"meera"` without item assignment.</x:v>
+The current code discards the cleaned result and incorrectly stores `True` in `has_name`. Which smallest repair creates the intended state?</x:v>
       </x:c>
       <x:c r="C4" t="str">
-        <x:v>Strings are immutable; slicing and concatenation build a new string that can be reassigned.</x:v>
+        <x:v>Reassignment retains the empty result of stripping the spaces, after which `bool(name)` correctly produces `False`.</x:v>
       </x:c>
       <x:c r="D4" t="n">
-        <x:v>10</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="E4" t="str">
         <x:v>published</x:v>
       </x:c>
       <x:c r="F4" t="str">
-        <x:v>hard</x:v>
+        <x:v>medium</x:v>
       </x:c>
       <x:c r="G4" t="str">
-        <x:v>evaluate</x:v>
+        <x:v>analyze</x:v>
       </x:c>
       <x:c r="H4" t="str">
         <x:v>python - Set 1</x:v>
@@ -568,52 +569,54 @@
         <x:v>strings</x:v>
       </x:c>
       <x:c r="K4" t="str">
-        <x:v>string-basics</x:v>
+        <x:v>string-methods</x:v>
       </x:c>
       <x:c r="L4"/>
       <x:c r="M4" t="str">
-        <x:v>`username = "m" + username[1:]`</x:v>
+        <x:v>Replace `name.strip()` with `name = name.strip()` before calculating `has_name`</x:v>
       </x:c>
       <x:c r="N4" t="str">
-        <x:v>`username[0].replace("n", "m")`</x:v>
+        <x:v>Replace `bool(name)` with `len(name) &gt; 0` without storing the stripped result</x:v>
       </x:c>
       <x:c r="O4" t="str">
-        <x:v>`username[0] == "m"`</x:v>
+        <x:v>Replace `name.strip()` with `name.upper()`</x:v>
       </x:c>
       <x:c r="P4" t="str">
-        <x:v>`username.insert(0, "m")`</x:v>
+        <x:v>Set `has_name = True` whenever the original input contains characters</x:v>
       </x:c>
       <x:c r="Q4" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="5" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="5" ht="158.39999389648438" hidden="0" customHeight="1">
       <x:c r="A5" t="str">
         <x:v>Python - MCQ - 5.1.4</x:v>
       </x:c>
       <x:c r="B5" t="str">
-        <x:v>A marketplace receives comma-separated tags and must rebuild the cleaned pieces as one hyphenated slug.
+        <x:v>Selecting the input that exposes a faulty email search
+A signup form uses the integer returned by `.find()` directly as a Boolean:
 ```python
-tags = "craft, gifts, pune"
-pieces = tags.split(", ")
-hashtag = __________
+if email.find("@"):
+    status = "Accepted"
+else:
+    status = "Rejected"
 ```
-The final value must be `"craft-gifts-pune"`.</x:v>
+The policy requires an at sign anywhere in the address. Which input most clearly proves that the implementation can accept an address containing no at sign?</x:v>
       </x:c>
       <x:c r="C5" t="str">
-        <x:v>The separator calls `join()` on the collection of string pieces.</x:v>
+        <x:v>An absent at sign makes `.find()` return `-1`, and `-1` is truthy, so the faulty condition accepts the invalid input.</x:v>
       </x:c>
       <x:c r="D5" t="n">
-        <x:v>8</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E5" t="str">
         <x:v>published</x:v>
       </x:c>
       <x:c r="F5" t="str">
-        <x:v>medium</x:v>
+        <x:v>hard</x:v>
       </x:c>
       <x:c r="G5" t="str">
-        <x:v>apply</x:v>
+        <x:v>evaluate</x:v>
       </x:c>
       <x:c r="H5" t="str">
         <x:v>python - Set 1</x:v>
@@ -625,47 +628,56 @@
         <x:v>strings</x:v>
       </x:c>
       <x:c r="K5" t="str">
-        <x:v>split-and-join</x:v>
+        <x:v>searching-and-membership</x:v>
       </x:c>
       <x:c r="L5"/>
       <x:c r="M5" t="str">
-        <x:v>`pieces.join("-")`</x:v>
+        <x:v>`"a@b.com"`</x:v>
       </x:c>
       <x:c r="N5" t="str">
-        <x:v>`tags.join(pieces)`</x:v>
+        <x:v>`"meera@shop.in"`</x:v>
       </x:c>
       <x:c r="O5" t="str">
-        <x:v>`"-".join(pieces)`</x:v>
+        <x:v>`"meerashop.in"`</x:v>
       </x:c>
       <x:c r="P5" t="str">
-        <x:v>`pieces.split("-")`</x:v>
+        <x:v>`"x@y"`</x:v>
       </x:c>
       <x:c r="Q5" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>
-    <x:row r="6" ht="39.599998474121094" hidden="0" customHeight="1">
+    <x:row r="6" ht="224.39999389648438" hidden="0" customHeight="1">
       <x:c r="A6" t="str">
         <x:v>Python - MCQ - 5.1.5</x:v>
       </x:c>
       <x:c r="B6" t="str">
-        <x:v>A caption analyser searches for an optional coupon code that may legitimately be absent.
-An optional coupon code may be absent from a caption. The program needs its first position when present and a non-crashing sentinel when absent. Select the correct operation.</x:v>
+        <x:v>Checking whether two slug builders are equivalent
+Two developers convert comma-separated tags into a hyphenated slug.
+Version A:
+```python
+slug = "-".join(tags.split(","))
+```
+Version B:
+```python
+slug = tags.replace(",", "-")
+```
+Assume `tags` is always a string. Which equivalence finding is correct, including for adjacent or trailing commas?</x:v>
       </x:c>
       <x:c r="C6" t="str">
-        <x:v>`find()` reports the first index or `-1`; `index()` raises an error when the text is missing.</x:v>
+        <x:v>Splitting on an explicit comma preserves empty pieces, and joining places one hyphen at every former comma boundary, exactly like `replace`.</x:v>
       </x:c>
       <x:c r="D6" t="n">
-        <x:v>10</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="E6" t="str">
         <x:v>published</x:v>
       </x:c>
       <x:c r="F6" t="str">
-        <x:v>hard</x:v>
+        <x:v>medium</x:v>
       </x:c>
       <x:c r="G6" t="str">
-        <x:v>evaluate</x:v>
+        <x:v>apply</x:v>
       </x:c>
       <x:c r="H6" t="str">
         <x:v>python - Set 1</x:v>
@@ -677,51 +689,51 @@
         <x:v>strings</x:v>
       </x:c>
       <x:c r="K6" t="str">
-        <x:v>searching-and-membership</x:v>
+        <x:v>split-and-join</x:v>
       </x:c>
       <x:c r="L6"/>
       <x:c r="M6" t="str">
-        <x:v>`caption.index(code)` because it returns zero when absent</x:v>
+        <x:v>Version A deletes empty pieces, so the versions differ whenever commas touch</x:v>
       </x:c>
       <x:c r="N6" t="str">
-        <x:v>`caption.count(code)` because it returns the position</x:v>
+        <x:v>Both replace every comma boundary with one hyphen and produce the same string for every `tags` value</x:v>
       </x:c>
       <x:c r="O6" t="str">
-        <x:v>`caption.find(code)` because it returns `-1` when absent</x:v>
+        <x:v>Version B replaces only the first comma</x:v>
       </x:c>
       <x:c r="P6" t="str">
-        <x:v>`code in caption` because it returns the position</x:v>
+        <x:v>They are equivalent only when `tags` contains exactly one comma</x:v>
       </x:c>
       <x:c r="Q6" t="n">
-        <x:v>3</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" ht="105.5999984741211" hidden="0" customHeight="1">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A7" t="str">
         <x:v>Python - MCQ - 5.1.6</x:v>
       </x:c>
       <x:c r="B7" t="str">
-        <x:v>A shop price list must display every amount with exactly two decimal places.
+        <x:v>Repairing a price that shows one decimal place
+A receipt stores `price = 49.5` but currently displays `₹49.5`:
 ```python
-price = 49.5
-display = f"₹{price:_____}"
+line = f"₹{price:.1f}"
 ```
-The required display is `₹49.50`.</x:v>
+Which smallest format-specifier repair produces the required `₹49.50` while leaving the numeric value unchanged?</x:v>
       </x:c>
       <x:c r="C7" t="str">
-        <x:v>`.2f` formats a numeric value with exactly two decimal places.</x:v>
+        <x:v>Changing `.1f` to `.2f` preserves the value and displays exactly two digits after the decimal point.</x:v>
       </x:c>
       <x:c r="D7" t="n">
-        <x:v>5</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="E7" t="str">
         <x:v>published</x:v>
       </x:c>
       <x:c r="F7" t="str">
-        <x:v>easy</x:v>
+        <x:v>medium</x:v>
       </x:c>
       <x:c r="G7" t="str">
-        <x:v>apply</x:v>
+        <x:v>evaluate</x:v>
       </x:c>
       <x:c r="H7" t="str">
         <x:v>python - Set 1</x:v>
@@ -737,16 +749,16 @@
       </x:c>
       <x:c r="L7"/>
       <x:c r="M7" t="str">
-        <x:v>`.2f`</x:v>
+        <x:v>`line = f"₹{price:.2f}"`</x:v>
       </x:c>
       <x:c r="N7" t="str">
-        <x:v>`2`</x:v>
+        <x:v>`line = f"₹{price:2}"`</x:v>
       </x:c>
       <x:c r="O7" t="str">
-        <x:v>`.2%`</x:v>
+        <x:v>`line = f"₹{price:.2%}"`</x:v>
       </x:c>
       <x:c r="P7" t="str">
-        <x:v>`,`</x:v>
+        <x:v>`line = f"₹{price:,}"`</x:v>
       </x:c>
       <x:c r="Q7" t="n">
         <x:v>1</x:v>
@@ -757,16 +769,16 @@
         <x:v>Python - MCQ - 5.1.7</x:v>
       </x:c>
       <x:c r="B8" t="str">
-        <x:v>A status panel needs two output lines and must preserve quotation marks around the readiness message.
-The output must be:
+        <x:v>Preserving a path and moving the filename to a new line
+A deployment note must display a Windows folder literally and place the filename on the next line:
 ```text
-Status
-"Ready"
+C:\new\table
+report.txt
 ```
-Select the valid one-line string literal.</x:v>
+Which assignment preserves the backslashes and inserts the required line break?</x:v>
       </x:c>
       <x:c r="C8" t="str">
-        <x:v>`\n` inserts the line break and `\"` preserves the double quotes inside the literal.</x:v>
+        <x:v>Doubled backslashes preserve the folder separators, while `\n` between the path and filename creates the required line break.</x:v>
       </x:c>
       <x:c r="D8" t="n">
         <x:v>8</x:v>
@@ -794,31 +806,38 @@
       </x:c>
       <x:c r="L8"/>
       <x:c r="M8" t="str">
-        <x:v>`message = "Status/n"Ready""`</x:v>
+        <x:v>`note = "C:\new\table report.txt"`</x:v>
       </x:c>
       <x:c r="N8" t="str">
-        <x:v>`message = "Status\tReady"`</x:v>
+        <x:v>`note = r"C:\new\table\nreport.txt"`</x:v>
       </x:c>
       <x:c r="O8" t="str">
-        <x:v>`message = "Status"\n"Ready""`</x:v>
+        <x:v>`note = "C:\new\table\nreport.txt"`</x:v>
       </x:c>
       <x:c r="P8" t="str">
-        <x:v>`message = "Status\n\"Ready\""`</x:v>
+        <x:v>`note = "C:\\new\\table\nreport.txt"`</x:v>
       </x:c>
       <x:c r="Q8" t="n">
         <x:v>4</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" ht="39.599998474121094" hidden="0" customHeight="1">
+    <x:row r="9" ht="158.39999389648438" hidden="0" customHeight="1">
       <x:c r="A9" t="str">
         <x:v>Python - MCQ - 5.1.8</x:v>
       </x:c>
       <x:c r="B9" t="str">
-        <x:v>A marketplace import contains outer spaces, inconsistent capitalisation, and comma-separated categories.
-Input arrives as `"  PYTHON, CRAFTS  "`. The required pieces are `['python', 'crafts']`. Which pipeline performs the operations in a sensible order?</x:v>
+        <x:v>Auditing a complete campaign-cleaning pipeline
+A campaign tool normalises a short message and prepares a compact summary:
+```python
+message = "  RED, blue,Red  "
+clean = message.strip().lower().replace(",", " ")
+words = clean.split()
+summary = f"{len(words)} words | red={clean.count('red')}"
+```
+Which summary reaches the audit log after every transformation?</x:v>
       </x:c>
       <x:c r="C9" t="str">
-        <x:v>Cleaning and normalising the string before splitting produces two lowercase pieces without outer whitespace.</x:v>
+        <x:v>Cleaning produces `"red  blue red"`; default splitting yields three words, and `red` occurs twice.</x:v>
       </x:c>
       <x:c r="D9" t="n">
         <x:v>10</x:v>
@@ -830,7 +849,7 @@
         <x:v>hard</x:v>
       </x:c>
       <x:c r="G9" t="str">
-        <x:v>evaluate</x:v>
+        <x:v>analyze</x:v>
       </x:c>
       <x:c r="H9" t="str">
         <x:v>python - Set 1</x:v>
@@ -846,34 +865,36 @@
       </x:c>
       <x:c r="L9"/>
       <x:c r="M9" t="str">
-        <x:v>Split on commas, then call `.lower()` on the resulting list.</x:v>
+        <x:v>`"4 words | red=1"`</x:v>
       </x:c>
       <x:c r="N9" t="str">
-        <x:v>Strip the text, lower it, then split on `", "`.</x:v>
+        <x:v>`"3 words | red=1"`</x:v>
       </x:c>
       <x:c r="O9" t="str">
-        <x:v>Join the original text, then strip the list.</x:v>
+        <x:v>`"3 words | red=2"`</x:v>
       </x:c>
       <x:c r="P9" t="str">
-        <x:v>Find the comma, discard everything after it, then uppercase.</x:v>
+        <x:v>`"4 words | red=2"`</x:v>
       </x:c>
       <x:c r="Q9" t="n">
-        <x:v>2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" ht="79.19999694824219" hidden="0" customHeight="1">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="132" hidden="0" customHeight="1">
       <x:c r="A10" t="str">
         <x:v>Python - MCQ - 5.1.9</x:v>
       </x:c>
       <x:c r="B10" t="str">
-        <x:v>A payment-confirmation screen reveals only the final four digits of a stored phone number.
+        <x:v>Editing one character of a locked string
+A developer tries to correct `"Nython"` using:
 ```python
-phone = "9876543210"
-last_four = __________
-```</x:v>
+word = "Nython"
+word[0] = "P"
+```
+Which review note accounts for the failed update?</x:v>
       </x:c>
       <x:c r="C10" t="str">
-        <x:v>A start of `-4` counts from the end, and an omitted stop continues through the final character.</x:v>
+        <x:v>Indexing can read a string but cannot assign into it because strings are immutable.</x:v>
       </x:c>
       <x:c r="D10" t="n">
         <x:v>5</x:v>
@@ -885,7 +906,7 @@
         <x:v>easy</x:v>
       </x:c>
       <x:c r="G10" t="str">
-        <x:v>apply</x:v>
+        <x:v>analyze</x:v>
       </x:c>
       <x:c r="H10" t="str">
         <x:v>python - Set 1</x:v>
@@ -897,39 +918,35 @@
         <x:v>strings</x:v>
       </x:c>
       <x:c r="K10" t="str">
-        <x:v>indexing-and-slicing</x:v>
+        <x:v>string-basics</x:v>
       </x:c>
       <x:c r="L10"/>
       <x:c r="M10" t="str">
-        <x:v>`phone[-4:]`</x:v>
+        <x:v>Strings do not support item assignment because they are immutable</x:v>
       </x:c>
       <x:c r="N10" t="str">
-        <x:v>`phone[4:]`</x:v>
+        <x:v>Index zero refers to the final character of a string</x:v>
       </x:c>
       <x:c r="O10" t="str">
-        <x:v>`phone[:-4]`</x:v>
+        <x:v>Only lowercase replacement characters are allowed</x:v>
       </x:c>
       <x:c r="P10" t="str">
-        <x:v>`phone[-1:4]`</x:v>
+        <x:v>Square brackets can be used only with numeric values, so text must be converted before editing</x:v>
       </x:c>
       <x:c r="Q10" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="11" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="11" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A11" t="str">
         <x:v>Python - MCQ - 5.1.10</x:v>
       </x:c>
       <x:c r="B11" t="str">
-        <x:v>An email-import service must trim accidental spaces, normalise capitalisation, and retain the cleaned result.
-```python
-email = "  ASHA@EXAMPLE.COM  "
-__________
-```
-The variable itself must become `"asha@example.com"`.</x:v>
+        <x:v>Rebuilding a misspelled language name
+A code label contains `word = "Nython"`. Which assignment creates `"Python"` without attempting to mutate the original string object?</x:v>
       </x:c>
       <x:c r="C11" t="str">
-        <x:v>Both methods return new strings, so the chained result must be reassigned.</x:v>
+        <x:v>The expression builds a new string from `"P"` and the unchanged slice `"ython"`.</x:v>
       </x:c>
       <x:c r="D11" t="n">
         <x:v>8</x:v>
@@ -941,7 +958,7 @@
         <x:v>medium</x:v>
       </x:c>
       <x:c r="G11" t="str">
-        <x:v>apply</x:v>
+        <x:v>evaluate</x:v>
       </x:c>
       <x:c r="H11" t="str">
         <x:v>python - Set 1</x:v>
@@ -953,259 +970,258 @@
         <x:v>strings</x:v>
       </x:c>
       <x:c r="K11" t="str">
-        <x:v>string-methods</x:v>
+        <x:v>indexing-and-slicing</x:v>
       </x:c>
       <x:c r="L11"/>
       <x:c r="M11" t="str">
-        <x:v>`email.strip().lower()`</x:v>
+        <x:v>`word[0] = "P"`</x:v>
       </x:c>
       <x:c r="N11" t="str">
-        <x:v>`email = email.strip`</x:v>
+        <x:v>`word = word[0] + "P"`</x:v>
       </x:c>
       <x:c r="O11" t="str">
-        <x:v>`email = email.strip().lower()`</x:v>
+        <x:v>`word = "P" + word[1:]`</x:v>
       </x:c>
       <x:c r="P11" t="str">
-        <x:v>`email.lower = email.strip()`</x:v>
+        <x:v>`word = word[:-1] + "P"`</x:v>
       </x:c>
       <x:c r="Q11" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>
-    <x:row r="12" ht="79.19999694824219" hidden="0" customHeight="1">
+    <x:row r="12" ht="145.1999969482422" hidden="0" customHeight="1">
       <x:c r="A12" t="str">
         <x:v>Python - MCQ - 5.2.1</x:v>
       </x:c>
       <x:c r="B12" t="str">
-        <x:v>A profile form counts every character in a short greeting, including the space between words.
-```python
-text = "Hi all"
-size = len(text)
-```</x:v>
-      </x:c>
-      <x:c r="C12" t="str">
-        <x:v>Two letters, one space, and three more letters make six characters.</x:v>
-      </x:c>
-      <x:c r="D12" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="E12" t="str">
-        <x:v>published</x:v>
-      </x:c>
-      <x:c r="F12" t="str">
-        <x:v>easy</x:v>
-      </x:c>
-      <x:c r="G12" t="str">
-        <x:v>apply</x:v>
-      </x:c>
-      <x:c r="H12" t="str">
-        <x:v>python - Set 2</x:v>
-      </x:c>
-      <x:c r="I12" t="str">
-        <x:v>python</x:v>
-      </x:c>
-      <x:c r="J12" t="str">
-        <x:v>strings</x:v>
-      </x:c>
-      <x:c r="K12" t="str">
-        <x:v>string-basics</x:v>
-      </x:c>
-      <x:c r="L12"/>
-      <x:c r="M12" t="str">
-        <x:v>`4`</x:v>
-      </x:c>
-      <x:c r="N12" t="str">
-        <x:v>`5`</x:v>
-      </x:c>
-      <x:c r="O12" t="str">
-        <x:v>`7`</x:v>
-      </x:c>
-      <x:c r="P12" t="str">
-        <x:v>`6`</x:v>
-      </x:c>
-      <x:c r="Q12" t="n">
-        <x:v>4</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" ht="39.599998474121094" hidden="0" customHeight="1">
-      <x:c r="A13" t="str">
-        <x:v>Python - MCQ - 5.2.2</x:v>
-      </x:c>
-      <x:c r="B13" t="str">
-        <x:v>A coupon service extracts a middle section of a code and must respect Python's exclusive slice boundary.
-For `word = "Python"`, complete the map: `word[1:4]` selects indices _____ and produces _____.</x:v>
-      </x:c>
-      <x:c r="C13" t="str">
-        <x:v>Slicing includes the start index and excludes the stop index.</x:v>
-      </x:c>
-      <x:c r="D13" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="E13" t="str">
-        <x:v>published</x:v>
-      </x:c>
-      <x:c r="F13" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="G13" t="str">
-        <x:v>apply</x:v>
-      </x:c>
-      <x:c r="H13" t="str">
-        <x:v>python - Set 2</x:v>
-      </x:c>
-      <x:c r="I13" t="str">
-        <x:v>python</x:v>
-      </x:c>
-      <x:c r="J13" t="str">
-        <x:v>strings</x:v>
-      </x:c>
-      <x:c r="K13" t="str">
-        <x:v>indexing-and-slicing</x:v>
-      </x:c>
-      <x:c r="L13"/>
-      <x:c r="M13" t="str">
-        <x:v>`1, 2, 3, 4`; `"ytho"`</x:v>
-      </x:c>
-      <x:c r="N13" t="str">
-        <x:v>`1, 2, 3`; `"yth"`</x:v>
-      </x:c>
-      <x:c r="O13" t="str">
-        <x:v>`0, 1, 2, 3`; `"Pyth"`</x:v>
-      </x:c>
-      <x:c r="P13" t="str">
-        <x:v>`1, 4`; `"yo"`</x:v>
-      </x:c>
-      <x:c r="Q13" t="n">
-        <x:v>2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" ht="79.19999694824219" hidden="0" customHeight="1">
-      <x:c r="A14" t="str">
-        <x:v>Python - MCQ - 5.2.3</x:v>
-      </x:c>
-      <x:c r="B14" t="str">
-        <x:v>A warehouse needs a product code displayed in reverse without writing a manual loop.
-```python
-code = "ABCD"
-reversed_code = code[__________]
-```</x:v>
-      </x:c>
-      <x:c r="C14" t="str">
-        <x:v>A step of `-1` traverses the full string from end to start.</x:v>
-      </x:c>
-      <x:c r="D14" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="E14" t="str">
-        <x:v>published</x:v>
-      </x:c>
-      <x:c r="F14" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="G14" t="str">
-        <x:v>apply</x:v>
-      </x:c>
-      <x:c r="H14" t="str">
-        <x:v>python - Set 2</x:v>
-      </x:c>
-      <x:c r="I14" t="str">
-        <x:v>python</x:v>
-      </x:c>
-      <x:c r="J14" t="str">
-        <x:v>strings</x:v>
-      </x:c>
-      <x:c r="K14" t="str">
-        <x:v>indexing-and-slicing</x:v>
-      </x:c>
-      <x:c r="L14"/>
-      <x:c r="M14" t="str">
-        <x:v>`-1`</x:v>
-      </x:c>
-      <x:c r="N14" t="str">
-        <x:v>`1:-1`</x:v>
-      </x:c>
-      <x:c r="O14" t="str">
-        <x:v>`::-1`</x:v>
-      </x:c>
-      <x:c r="P14" t="str">
-        <x:v>`-1:0`</x:v>
-      </x:c>
-      <x:c r="Q14" t="n">
-        <x:v>3</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" ht="118.80000305175781" hidden="0" customHeight="1">
-      <x:c r="A15" t="str">
-        <x:v>Python - MCQ - 5.2.4</x:v>
-      </x:c>
-      <x:c r="B15" t="str">
-        <x:v>A preview service is being tested with requests that extend beyond a short word's available characters.
-```python
-word = "cat"
-one = word[10]
-two = word[:10]
-```
-Which review statement is accurate?</x:v>
-      </x:c>
-      <x:c r="C15" t="str">
-        <x:v>A single invalid index fails, while slice boundaries are safely limited to the available string.</x:v>
-      </x:c>
-      <x:c r="D15" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="E15" t="str">
-        <x:v>published</x:v>
-      </x:c>
-      <x:c r="F15" t="str">
-        <x:v>hard</x:v>
-      </x:c>
-      <x:c r="G15" t="str">
-        <x:v>evaluate</x:v>
-      </x:c>
-      <x:c r="H15" t="str">
-        <x:v>python - Set 2</x:v>
-      </x:c>
-      <x:c r="I15" t="str">
-        <x:v>python</x:v>
-      </x:c>
-      <x:c r="J15" t="str">
-        <x:v>strings</x:v>
-      </x:c>
-      <x:c r="K15" t="str">
-        <x:v>indexing-and-slicing</x:v>
-      </x:c>
-      <x:c r="L15"/>
-      <x:c r="M15" t="str">
-        <x:v>`word[10]` raises `IndexError`, while `word[:10]` safely returns `"cat"`.</x:v>
-      </x:c>
-      <x:c r="N15" t="str">
-        <x:v>Both expressions return `""`.</x:v>
-      </x:c>
-      <x:c r="O15" t="str">
-        <x:v>Both expressions raise `IndexError`.</x:v>
-      </x:c>
-      <x:c r="P15" t="str">
-        <x:v>`word[10]` returns `"t"`, while the slice raises an error.</x:v>
-      </x:c>
-      <x:c r="Q15" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" ht="118.80000305175781" hidden="0" customHeight="1">
-      <x:c r="A16" t="str">
-        <x:v>Python - MCQ - 5.2.5</x:v>
-      </x:c>
-      <x:c r="B16" t="str">
-        <x:v>A user-profile cleanup calls an uppercase method, but the displayed name remains unchanged.
+        <x:v>An uppercase result is discarded
+A profile service runs:
 ```python
 name = "asha"
 name.upper()
 print(name)
 ```
-Complete the reviewer note.</x:v>
+The screen still shows lowercase text. Which explanation should appear in the review?</x:v>
+      </x:c>
+      <x:c r="C12" t="str">
+        <x:v>Transforming methods return a new string; ignoring the return value leaves the original variable unchanged.</x:v>
+      </x:c>
+      <x:c r="D12" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="E12" t="str">
+        <x:v>published</x:v>
+      </x:c>
+      <x:c r="F12" t="str">
+        <x:v>easy</x:v>
+      </x:c>
+      <x:c r="G12" t="str">
+        <x:v>analyze</x:v>
+      </x:c>
+      <x:c r="H12" t="str">
+        <x:v>python - Set 2</x:v>
+      </x:c>
+      <x:c r="I12" t="str">
+        <x:v>python</x:v>
+      </x:c>
+      <x:c r="J12" t="str">
+        <x:v>strings</x:v>
+      </x:c>
+      <x:c r="K12" t="str">
+        <x:v>string-methods</x:v>
+      </x:c>
+      <x:c r="L12"/>
+      <x:c r="M12" t="str">
+        <x:v>`upper()` changes only the first character</x:v>
+      </x:c>
+      <x:c r="N12" t="str">
+        <x:v>The method returned a new string, but no variable stored that result</x:v>
+      </x:c>
+      <x:c r="O12" t="str">
+        <x:v>Printing converts uppercase strings back to lowercase</x:v>
+      </x:c>
+      <x:c r="P12" t="str">
+        <x:v>String methods work only on text entered with `input()` and cannot transform literals or stored variables</x:v>
+      </x:c>
+      <x:c r="Q12" t="n">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="132" hidden="0" customHeight="1">
+      <x:c r="A13" t="str">
+        <x:v>Python - MCQ - 5.2.2</x:v>
+      </x:c>
+      <x:c r="B13" t="str">
+        <x:v>Original and transformed captions remain separate
+A moderation tool keeps both versions:
+```python
+original = "summer sale"
+display = original.title()
+```
+Which pair should the audit report contain?</x:v>
+      </x:c>
+      <x:c r="C13" t="str">
+        <x:v>`title()` produces a new value for `display` and does not modify `original`.</x:v>
+      </x:c>
+      <x:c r="D13" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E13" t="str">
+        <x:v>published</x:v>
+      </x:c>
+      <x:c r="F13" t="str">
+        <x:v>hard</x:v>
+      </x:c>
+      <x:c r="G13" t="str">
+        <x:v>analyze</x:v>
+      </x:c>
+      <x:c r="H13" t="str">
+        <x:v>python - Set 2</x:v>
+      </x:c>
+      <x:c r="I13" t="str">
+        <x:v>python</x:v>
+      </x:c>
+      <x:c r="J13" t="str">
+        <x:v>strings</x:v>
+      </x:c>
+      <x:c r="K13" t="str">
+        <x:v>string-methods</x:v>
+      </x:c>
+      <x:c r="L13"/>
+      <x:c r="M13" t="str">
+        <x:v>`original = "Summer Sale"`, `display = "Summer Sale"`</x:v>
+      </x:c>
+      <x:c r="N13" t="str">
+        <x:v>`original = "summer sale"`, `display = "summer sale"`</x:v>
+      </x:c>
+      <x:c r="O13" t="str">
+        <x:v>Both variables become empty after the method call</x:v>
+      </x:c>
+      <x:c r="P13" t="str">
+        <x:v>`original = "summer sale"`, `display = "Summer Sale"`</x:v>
+      </x:c>
+      <x:c r="Q13" t="n">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="39.599998474121094" hidden="0" customHeight="1">
+      <x:c r="A14" t="str">
+        <x:v>Python - MCQ - 5.2.3</x:v>
+      </x:c>
+      <x:c r="B14" t="str">
+        <x:v>Normalising an email before comparison
+A login field may contain capital letters and accidental spaces at both ends. Which expression produces a trimmed, lowercase version for comparison?</x:v>
+      </x:c>
+      <x:c r="C14" t="str">
+        <x:v>`strip()` removes surrounding whitespace and `lower()` normalises the remaining characters.</x:v>
+      </x:c>
+      <x:c r="D14" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="E14" t="str">
+        <x:v>published</x:v>
+      </x:c>
+      <x:c r="F14" t="str">
+        <x:v>easy</x:v>
+      </x:c>
+      <x:c r="G14" t="str">
+        <x:v>evaluate</x:v>
+      </x:c>
+      <x:c r="H14" t="str">
+        <x:v>python - Set 2</x:v>
+      </x:c>
+      <x:c r="I14" t="str">
+        <x:v>python</x:v>
+      </x:c>
+      <x:c r="J14" t="str">
+        <x:v>strings</x:v>
+      </x:c>
+      <x:c r="K14" t="str">
+        <x:v>string-methods</x:v>
+      </x:c>
+      <x:c r="L14"/>
+      <x:c r="M14" t="str">
+        <x:v>`email.upper().strip()`</x:v>
+      </x:c>
+      <x:c r="N14" t="str">
+        <x:v>`email.replace(" ", "_")`</x:v>
+      </x:c>
+      <x:c r="O14" t="str">
+        <x:v>`email.strip().lower()`</x:v>
+      </x:c>
+      <x:c r="P14" t="str">
+        <x:v>`email.title()`</x:v>
+      </x:c>
+      <x:c r="Q14" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="118.80000305175781" hidden="0" customHeight="1">
+      <x:c r="A15" t="str">
+        <x:v>Python - MCQ - 5.2.4</x:v>
+      </x:c>
+      <x:c r="B15" t="str">
+        <x:v>Replacing every matching letter
+A word-game hint applies:
+```python
+hint = "banana".replace("a", "o")
+```
+Which hint is stored?</x:v>
+      </x:c>
+      <x:c r="C15" t="str">
+        <x:v>`replace` swaps every lowercase `a`, producing `"bonono"`.</x:v>
+      </x:c>
+      <x:c r="D15" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="E15" t="str">
+        <x:v>published</x:v>
+      </x:c>
+      <x:c r="F15" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="G15" t="str">
+        <x:v>apply</x:v>
+      </x:c>
+      <x:c r="H15" t="str">
+        <x:v>python - Set 2</x:v>
+      </x:c>
+      <x:c r="I15" t="str">
+        <x:v>python</x:v>
+      </x:c>
+      <x:c r="J15" t="str">
+        <x:v>strings</x:v>
+      </x:c>
+      <x:c r="K15" t="str">
+        <x:v>string-methods</x:v>
+      </x:c>
+      <x:c r="L15"/>
+      <x:c r="M15" t="str">
+        <x:v>`"bonana"`</x:v>
+      </x:c>
+      <x:c r="N15" t="str">
+        <x:v>`"bonono"`</x:v>
+      </x:c>
+      <x:c r="O15" t="str">
+        <x:v>`"banana"`</x:v>
+      </x:c>
+      <x:c r="P15" t="str">
+        <x:v>`"booooo"`</x:v>
+      </x:c>
+      <x:c r="Q15" t="n">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="39.599998474121094" hidden="0" customHeight="1">
+      <x:c r="A16" t="str">
+        <x:v>Python - MCQ - 5.2.5</x:v>
+      </x:c>
+      <x:c r="B16" t="str">
+        <x:v>A decimal point fails a digit-only check
+A form receives `raw_price = "12.5"` and evaluates `raw_price.isdigit()`. Which validation result should the team expect?</x:v>
       </x:c>
       <x:c r="C16" t="str">
-        <x:v>Transforming string methods do not mutate the original value.</x:v>
+        <x:v>`.isdigit()` requires every character to be a digit, and the decimal point fails that test.</x:v>
       </x:c>
       <x:c r="D16" t="n">
         <x:v>8</x:v>
@@ -1217,7 +1233,7 @@
         <x:v>medium</x:v>
       </x:c>
       <x:c r="G16" t="str">
-        <x:v>evaluate</x:v>
+        <x:v>analyze</x:v>
       </x:c>
       <x:c r="H16" t="str">
         <x:v>python - Set 2</x:v>
@@ -1233,46 +1249,43 @@
       </x:c>
       <x:c r="L16"/>
       <x:c r="M16" t="str">
-        <x:v>`upper()` fails because lowercase text is immutable.</x:v>
+        <x:v>`True`, because the text represents a numeric value</x:v>
       </x:c>
       <x:c r="N16" t="str">
-        <x:v>`upper()` returned a new string that was not stored, so `name` remains `"asha"`.</x:v>
+        <x:v>`True`, because punctuation is ignored by `isdigit()`</x:v>
       </x:c>
       <x:c r="O16" t="str">
-        <x:v>`print()` automatically converts text back to lowercase.</x:v>
+        <x:v>A conversion error before any Boolean is produced</x:v>
       </x:c>
       <x:c r="P16" t="str">
-        <x:v>`upper()` changes only the first character.</x:v>
+        <x:v>`False`, because the decimal point is not a digit</x:v>
       </x:c>
       <x:c r="Q16" t="n">
-        <x:v>2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" ht="79.19999694824219" hidden="0" customHeight="1">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A17" t="str">
         <x:v>Python - MCQ - 5.2.6</x:v>
       </x:c>
       <x:c r="B17" t="str">
-        <x:v>A product catalogue replaces an old term everywhere it occurs, including inside a longer word.
-```python
-text = "tea team"
-changed = text.replace("tea", "art")
-```</x:v>
+        <x:v>Capturing every cleanup step
+A customer name arrives as `"   meera shah   "`. The stored value must become `"Meera Shah"`. Which one-line repair both transforms and retains the cleaned result?</x:v>
       </x:c>
       <x:c r="C17" t="str">
-        <x:v>`replace()` changes every non-overlapping occurrence of `"tea"`, including the start of `"team"`.</x:v>
+        <x:v>The chained methods produce the required form, and reassignment retains the new string.</x:v>
       </x:c>
       <x:c r="D17" t="n">
-        <x:v>5</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E17" t="str">
         <x:v>published</x:v>
       </x:c>
       <x:c r="F17" t="str">
-        <x:v>easy</x:v>
+        <x:v>hard</x:v>
       </x:c>
       <x:c r="G17" t="str">
-        <x:v>apply</x:v>
+        <x:v>evaluate</x:v>
       </x:c>
       <x:c r="H17" t="str">
         <x:v>python - Set 2</x:v>
@@ -1288,46 +1301,43 @@
       </x:c>
       <x:c r="L17"/>
       <x:c r="M17" t="str">
-        <x:v>`"art team"`</x:v>
+        <x:v>`name = name.strip().title()`</x:v>
       </x:c>
       <x:c r="N17" t="str">
-        <x:v>`"tea artm"`</x:v>
+        <x:v>`name.strip().title()`</x:v>
       </x:c>
       <x:c r="O17" t="str">
-        <x:v>`"art"`</x:v>
+        <x:v>`name = name.upper().replace(" ", "")`</x:v>
       </x:c>
       <x:c r="P17" t="str">
-        <x:v>`"art artm"`</x:v>
+        <x:v>`name = name.lower().rstrip()`</x:v>
       </x:c>
       <x:c r="Q17" t="n">
-        <x:v>4</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="79.19999694824219" hidden="0" customHeight="1">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A18" t="str">
         <x:v>Python - MCQ - 5.2.7</x:v>
       </x:c>
       <x:c r="B18" t="str">
-        <x:v>A weather form uses `.isdigit()` to inspect a signed temperature entered as text.
-```python
-raw = "-5"
-valid = raw.isdigit()
-```</x:v>
+        <x:v>Turning one tag line into three values
+A craft form stores `tags = "handmade,gifts,pune"`. Which expression separates it at the commas?</x:v>
       </x:c>
       <x:c r="C18" t="str">
-        <x:v>`.isdigit()` inspects characters; the leading minus sign causes the check to return false.</x:v>
+        <x:v>`split(",")` cuts the original string wherever a comma occurs.</x:v>
       </x:c>
       <x:c r="D18" t="n">
-        <x:v>8</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E18" t="str">
         <x:v>published</x:v>
       </x:c>
       <x:c r="F18" t="str">
-        <x:v>medium</x:v>
+        <x:v>easy</x:v>
       </x:c>
       <x:c r="G18" t="str">
-        <x:v>analyze</x:v>
+        <x:v>evaluate</x:v>
       </x:c>
       <x:c r="H18" t="str">
         <x:v>python - Set 2</x:v>
@@ -1339,48 +1349,48 @@
         <x:v>strings</x:v>
       </x:c>
       <x:c r="K18" t="str">
-        <x:v>string-methods</x:v>
+        <x:v>split-and-join</x:v>
       </x:c>
       <x:c r="L18"/>
       <x:c r="M18" t="str">
-        <x:v>`valid` is `False` because the minus sign is not a digit.</x:v>
+        <x:v>`tags.join(",")`, because `join` separates text</x:v>
       </x:c>
       <x:c r="N18" t="str">
-        <x:v>`valid` is `True` because `-5` is numerically valid.</x:v>
+        <x:v>`tags.split()`</x:v>
       </x:c>
       <x:c r="O18" t="str">
-        <x:v>`.isdigit()` converts the text to integer `-5`.</x:v>
+        <x:v>`",".join(tags)`</x:v>
       </x:c>
       <x:c r="P18" t="str">
-        <x:v>Python raises `ValueError` inside `.isdigit()`.</x:v>
+        <x:v>`tags.split(",")`</x:v>
       </x:c>
       <x:c r="Q18" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" ht="105.5999984741211" hidden="0" customHeight="1">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A19" t="str">
         <x:v>Python - MCQ - 5.2.8</x:v>
       </x:c>
       <x:c r="B19" t="str">
-        <x:v>A report builder tries to join numeric identifiers with hyphens before converting them to strings.
+        <x:v>Several spaces still represent one boundary
+A sentence contains irregular spacing:
 ```python
-parts = [10, 20, 30]
-result = "-".join(parts)
+words = "fresh   handmade  gifts".split()
 ```
-Select the correct diagnosis.</x:v>
+Which list structure is produced by the default split behavior?</x:v>
       </x:c>
       <x:c r="C19" t="str">
-        <x:v>The separator can be any string, but every joined element must already be a string.</x:v>
+        <x:v>With no argument, `split()` treats runs of whitespace as separators and does not create empty pieces.</x:v>
       </x:c>
       <x:c r="D19" t="n">
-        <x:v>10</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="E19" t="str">
         <x:v>published</x:v>
       </x:c>
       <x:c r="F19" t="str">
-        <x:v>hard</x:v>
+        <x:v>medium</x:v>
       </x:c>
       <x:c r="G19" t="str">
         <x:v>analyze</x:v>
@@ -1399,19 +1409,19 @@
       </x:c>
       <x:c r="L19"/>
       <x:c r="M19" t="str">
-        <x:v>The hyphen cannot be used as a separator.</x:v>
+        <x:v>`['fresh', 'handmade', 'gifts']`</x:v>
       </x:c>
       <x:c r="N19" t="str">
-        <x:v>`join()` works only with an empty separator.</x:v>
+        <x:v>`['fresh', '', '', 'handmade', '', 'gifts']`</x:v>
       </x:c>
       <x:c r="O19" t="str">
-        <x:v>`join()` requires string pieces, but the collection contains integers.</x:v>
+        <x:v>`['fresh   handmade  gifts']`</x:v>
       </x:c>
       <x:c r="P19" t="str">
-        <x:v>The list must contain exactly two items.</x:v>
+        <x:v>`['fresh', '   ', 'handmade', '  ', 'gifts']`</x:v>
       </x:c>
       <x:c r="Q19" t="n">
-        <x:v>3</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="39.599998474121094" hidden="0" customHeight="1">
@@ -1419,11 +1429,11 @@
         <x:v>Python - MCQ - 5.2.9</x:v>
       </x:c>
       <x:c r="B20" t="str">
-        <x:v>A caption parser must treat several consecutive spaces as one word boundary.
-The text is `"red   blue"` with three spaces. Which statement is correct?</x:v>
+        <x:v>Constructing a URL-friendly tag
+A page has `parts = ["handmade", "gifts", "pune"]` and needs `"handmade-gifts-pune"`. Which expression uses the intended separator?</x:v>
       </x:c>
       <x:c r="C20" t="str">
-        <x:v>Default splitting treats runs of whitespace as separators; an explicit single space cuts at each individual space.</x:v>
+        <x:v>`join` is called on the separator string and places that separator between all list items.</x:v>
       </x:c>
       <x:c r="D20" t="n">
         <x:v>8</x:v>
@@ -1435,7 +1445,7 @@
         <x:v>medium</x:v>
       </x:c>
       <x:c r="G20" t="str">
-        <x:v>analyze</x:v>
+        <x:v>apply</x:v>
       </x:c>
       <x:c r="H20" t="str">
         <x:v>python - Set 2</x:v>
@@ -1451,36 +1461,31 @@
       </x:c>
       <x:c r="L20"/>
       <x:c r="M20" t="str">
-        <x:v>`text.split()` keeps all empty pieces between spaces.</x:v>
+        <x:v>`parts.join("-")`</x:v>
       </x:c>
       <x:c r="N20" t="str">
-        <x:v>`text.split()` produces `['red', 'blue']`, while `text.split(' ')` can produce empty pieces.</x:v>
+        <x:v>`"".join(parts)`</x:v>
       </x:c>
       <x:c r="O20" t="str">
-        <x:v>Both calls return the original string.</x:v>
+        <x:v>`"-".join(parts)`</x:v>
       </x:c>
       <x:c r="P20" t="str">
-        <x:v>`text.split(' ')` removes the word `blue`.</x:v>
+        <x:v>`parts.split("-")`</x:v>
       </x:c>
       <x:c r="Q20" t="n">
-        <x:v>2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21" ht="118.80000305175781" hidden="0" customHeight="1">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A21" t="str">
         <x:v>Python - MCQ - 5.2.10</x:v>
       </x:c>
       <x:c r="B21" t="str">
-        <x:v>An email checker searches for a required at sign using a method that raises an error when the symbol is absent.
-```python
-email = "asha.example.com"
-position = email.index("@")
-status = "checked"
-```
-What happens before `status` is assigned?</x:v>
+        <x:v>Numeric IDs cannot be joined directly
+A report tries to build a code using `"-".join([10, 20, 30])` and is rejected. Which diagnosis guides the smallest appropriate redesign?</x:v>
       </x:c>
       <x:c r="C21" t="str">
-        <x:v>Unlike `find()`, `index()` does not return a sentinel for missing text; it raises an error.</x:v>
+        <x:v>`join` requires string pieces; integers need to be represented as strings before joining.</x:v>
       </x:c>
       <x:c r="D21" t="n">
         <x:v>10</x:v>
@@ -1492,7 +1497,7 @@
         <x:v>hard</x:v>
       </x:c>
       <x:c r="G21" t="str">
-        <x:v>analyze</x:v>
+        <x:v>evaluate</x:v>
       </x:c>
       <x:c r="H21" t="str">
         <x:v>python - Set 2</x:v>
@@ -1504,38 +1509,42 @@
         <x:v>strings</x:v>
       </x:c>
       <x:c r="K21" t="str">
-        <x:v>searching-and-membership</x:v>
+        <x:v>split-and-join</x:v>
       </x:c>
       <x:c r="L21"/>
       <x:c r="M21" t="str">
-        <x:v>`position` becomes `-1`.</x:v>
+        <x:v>Wrap the complete `join` call in `str()`; conversion after joining will make the integer elements acceptable</x:v>
       </x:c>
       <x:c r="N21" t="str">
-        <x:v>`position` becomes `0`.</x:v>
+        <x:v>Every joined piece must already be a string, so the numeric IDs need string representations</x:v>
       </x:c>
       <x:c r="O21" t="str">
-        <x:v>`position` becomes `None`.</x:v>
+        <x:v>Convert the entire list once with `str([10, 20, 30])` and pass that one string to `join`, which will preserve each ID as one piece</x:v>
       </x:c>
       <x:c r="P21" t="str">
-        <x:v>`index()` raises an error because `"@"` is absent.</x:v>
+        <x:v>Call `[10, 20, 30].join("-")` so the collection, rather than the separator, controls the operation</x:v>
       </x:c>
       <x:c r="Q21" t="n">
-        <x:v>4</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22" ht="79.19999694824219" hidden="0" customHeight="1">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" ht="158.39999389648438" hidden="0" customHeight="1">
       <x:c r="A22" t="str">
-        <x:v>Python - MCQ - 5.2.11</x:v>
+        <x:v>Python - MCQ - 5.3.1</x:v>
       </x:c>
       <x:c r="B22" t="str">
-        <x:v>A campaign tracker counts a keyword written with several different capitalisations.
+        <x:v>Completing a rough email membership condition
+A signup form needs a quick branch that accepts text containing an at sign anywhere:
 ```python
-text = "Sale sale SALE sale"
-matches = text.count("sale")
-```</x:v>
+if __________________:
+    status = "Continue"
+else:
+    status = "Missing @"
+```
+Which expression completes the condition directly without relying on a numeric search position?</x:v>
       </x:c>
       <x:c r="C22" t="str">
-        <x:v>Searching is case-sensitive, so only the two lowercase occurrences match exactly.</x:v>
+        <x:v>The `in` operator directly returns whether the at sign occurs anywhere in the email.</x:v>
       </x:c>
       <x:c r="D22" t="n">
         <x:v>5</x:v>
@@ -1550,7 +1559,7 @@
         <x:v>apply</x:v>
       </x:c>
       <x:c r="H22" t="str">
-        <x:v>python - Set 2</x:v>
+        <x:v>python - Set 3</x:v>
       </x:c>
       <x:c r="I22" t="str">
         <x:v>python</x:v>
@@ -1563,31 +1572,31 @@
       </x:c>
       <x:c r="L22"/>
       <x:c r="M22" t="str">
-        <x:v>`4`</x:v>
+        <x:v>`"@" in email`</x:v>
       </x:c>
       <x:c r="N22" t="str">
-        <x:v>`3`</x:v>
+        <x:v>`email.find("@")`</x:v>
       </x:c>
       <x:c r="O22" t="str">
-        <x:v>`2`</x:v>
+        <x:v>`email.count("@") + 1`</x:v>
       </x:c>
       <x:c r="P22" t="str">
-        <x:v>`1`</x:v>
+        <x:v>`email.startswith("@") and email.endswith("@")`</x:v>
       </x:c>
       <x:c r="Q22" t="n">
-        <x:v>3</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A23" t="str">
-        <x:v>Python - MCQ - 5.2.12</x:v>
+        <x:v>Python - MCQ - 5.3.2</x:v>
       </x:c>
       <x:c r="B23" t="str">
-        <x:v>An order-import tool accepts files only when their names use a required prefix and CSV suffix.
-A file is accepted when its lowercase name begins with `"order_"` and ends with `".csv"`. Select the clearest check.</x:v>
+        <x:v>Searching safely for an optional marker
+A tracking reference may or may not contain `"-"`. The program uses `reference.find("-")`. Which value signals that the marker is absent without raising an exception?</x:v>
       </x:c>
       <x:c r="C23" t="str">
-        <x:v>The two edge-specific methods directly express the prefix and suffix requirements after case normalisation.</x:v>
+        <x:v>`find` returns -1 when the searched text is absent.</x:v>
       </x:c>
       <x:c r="D23" t="n">
         <x:v>8</x:v>
@@ -1602,7 +1611,7 @@
         <x:v>apply</x:v>
       </x:c>
       <x:c r="H23" t="str">
-        <x:v>python - Set 2</x:v>
+        <x:v>python - Set 3</x:v>
       </x:c>
       <x:c r="I23" t="str">
         <x:v>python</x:v>
@@ -1615,49 +1624,46 @@
       </x:c>
       <x:c r="L23"/>
       <x:c r="M23" t="str">
-        <x:v>`name.lower().startswith("order_") and name.lower().endswith(".csv")`</x:v>
+        <x:v>`0`</x:v>
       </x:c>
       <x:c r="N23" t="str">
-        <x:v>`"order_" in name or ".csv" in name`</x:v>
+        <x:v>`False`</x:v>
       </x:c>
       <x:c r="O23" t="str">
-        <x:v>`name.find("order_") and name.find(".csv")`</x:v>
+        <x:v>`None`</x:v>
       </x:c>
       <x:c r="P23" t="str">
-        <x:v>`name.count("order_.csv") == 2`</x:v>
+        <x:v>`-1`</x:v>
       </x:c>
       <x:c r="Q23" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="24" ht="92.4000015258789" hidden="0" customHeight="1">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A24" t="str">
-        <x:v>Python - MCQ - 5.2.13</x:v>
+        <x:v>Python - MCQ - 5.3.3</x:v>
       </x:c>
       <x:c r="B24" t="str">
-        <x:v>A progress dashboard stores completion as a proportion but must present it as a readable percentage.
-```python
-completion = 0.873
-```
-The report must show `87.3%`. Select the correct f-string.</x:v>
+        <x:v>Case-sensitive sale counting
+A caption is `"Sale sale SALE"`. The analytics code uses `caption.count("sale")` without normalising case. Which count is recorded?</x:v>
       </x:c>
       <x:c r="C24" t="str">
-        <x:v>`.1%` multiplies the proportion by 100, uses one decimal place, and appends the percent sign.</x:v>
+        <x:v>Search is case-sensitive, so only the exact lowercase occurrence matches.</x:v>
       </x:c>
       <x:c r="D24" t="n">
-        <x:v>10</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="E24" t="str">
         <x:v>published</x:v>
       </x:c>
       <x:c r="F24" t="str">
-        <x:v>hard</x:v>
+        <x:v>medium</x:v>
       </x:c>
       <x:c r="G24" t="str">
         <x:v>apply</x:v>
       </x:c>
       <x:c r="H24" t="str">
-        <x:v>python - Set 2</x:v>
+        <x:v>python - Set 3</x:v>
       </x:c>
       <x:c r="I24" t="str">
         <x:v>python</x:v>
@@ -1666,53 +1672,56 @@
         <x:v>strings</x:v>
       </x:c>
       <x:c r="K24" t="str">
-        <x:v>string-formatting</x:v>
+        <x:v>searching-and-membership</x:v>
       </x:c>
       <x:c r="L24"/>
       <x:c r="M24" t="str">
-        <x:v>`f"{completion:.1f}%"`</x:v>
+        <x:v>`3`</x:v>
       </x:c>
       <x:c r="N24" t="str">
-        <x:v>`f"{completion:1%}"`</x:v>
+        <x:v>`1`</x:v>
       </x:c>
       <x:c r="O24" t="str">
-        <x:v>`f"{completion * 100:.1f}"`</x:v>
+        <x:v>`2`</x:v>
       </x:c>
       <x:c r="P24" t="str">
-        <x:v>`f"{completion:.1%}"`</x:v>
+        <x:v>`0`</x:v>
       </x:c>
       <x:c r="Q24" t="n">
-        <x:v>4</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="25" ht="79.19999694824219" hidden="0" customHeight="1">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" ht="158.39999389648438" hidden="0" customHeight="1">
       <x:c r="A25" t="str">
-        <x:v>Python - MCQ - 5.2.14</x:v>
+        <x:v>Python - MCQ - 5.3.4</x:v>
       </x:c>
       <x:c r="B25" t="str">
-        <x:v>A shop price list aligns item names into a fixed-width left-hand column.
+        <x:v>Tracing an upload rule with two required text checks
+A portal accepts an upload only when its name ends in `.jpg` regardless of case and its caption is not empty after surrounding spaces are removed:
 ```python
-item = "Clay"
-column = f"{item:_____}"
-```</x:v>
+filename = "PRODUCT.JPG"
+caption = "  Summer sale  "
+accepted = filename.lower().endswith(".jpg") and bool(caption.strip())
+```
+Which audit result correctly traces both requirements?</x:v>
       </x:c>
       <x:c r="C25" t="str">
-        <x:v>`&lt;10` left-aligns the text in a field with minimum width ten.</x:v>
+        <x:v>The lowercased filename ends in `.jpg`, and stripping leaves the non-empty caption `"Summer sale"`, so both sides of `and` are true.</x:v>
       </x:c>
       <x:c r="D25" t="n">
-        <x:v>5</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E25" t="str">
         <x:v>published</x:v>
       </x:c>
       <x:c r="F25" t="str">
-        <x:v>easy</x:v>
+        <x:v>hard</x:v>
       </x:c>
       <x:c r="G25" t="str">
-        <x:v>understand</x:v>
+        <x:v>apply</x:v>
       </x:c>
       <x:c r="H25" t="str">
-        <x:v>python - Set 2</x:v>
+        <x:v>python - Set 3</x:v>
       </x:c>
       <x:c r="I25" t="str">
         <x:v>python</x:v>
@@ -1721,50 +1730,50 @@
         <x:v>strings</x:v>
       </x:c>
       <x:c r="K25" t="str">
-        <x:v>string-formatting</x:v>
+        <x:v>searching-and-membership</x:v>
       </x:c>
       <x:c r="L25"/>
       <x:c r="M25" t="str">
-        <x:v>`&gt;10`</x:v>
+        <x:v>`False`, because lowercasing the filename changes the stored original</x:v>
       </x:c>
       <x:c r="N25" t="str">
-        <x:v>`&lt;10`</x:v>
+        <x:v>`False`, because `.strip()` always produces an empty string</x:v>
       </x:c>
       <x:c r="O25" t="str">
-        <x:v>`^2`</x:v>
+        <x:v>`True`, because the normalised filename has the required suffix and the cleaned caption is non-empty</x:v>
       </x:c>
       <x:c r="P25" t="str">
-        <x:v>`.10f`</x:v>
+        <x:v>`True`, because `and` needs only one side to succeed</x:v>
       </x:c>
       <x:c r="Q25" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A26" t="str">
-        <x:v>Python - MCQ - 5.2.15</x:v>
+        <x:v>Python - MCQ - 5.3.5</x:v>
       </x:c>
       <x:c r="B26" t="str">
-        <x:v>A configuration tool stores a Windows-style path whose backslashes must remain literal characters.
-The path must retain the characters in `C:\new\table` rather than interpret `\n` and `\t`.</x:v>
+        <x:v>Showing a price with two decimal places
+A product stores `price = 49.5`. Which f-string displays the customer-facing value as `₹49.50`?</x:v>
       </x:c>
       <x:c r="C26" t="str">
-        <x:v>The raw-string prefix tells Python to treat backslashes literally.</x:v>
+        <x:v>The `.2f` specifier displays a numeric value with exactly two digits after the decimal point.</x:v>
       </x:c>
       <x:c r="D26" t="n">
-        <x:v>8</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E26" t="str">
         <x:v>published</x:v>
       </x:c>
       <x:c r="F26" t="str">
-        <x:v>medium</x:v>
+        <x:v>easy</x:v>
       </x:c>
       <x:c r="G26" t="str">
         <x:v>evaluate</x:v>
       </x:c>
       <x:c r="H26" t="str">
-        <x:v>python - Set 2</x:v>
+        <x:v>python - Set 3</x:v>
       </x:c>
       <x:c r="I26" t="str">
         <x:v>python</x:v>
@@ -1773,35 +1782,35 @@
         <x:v>strings</x:v>
       </x:c>
       <x:c r="K26" t="str">
-        <x:v>escape-sequences</x:v>
+        <x:v>string-formatting</x:v>
       </x:c>
       <x:c r="L26"/>
       <x:c r="M26" t="str">
-        <x:v>`path = r"C:\new\table"`</x:v>
+        <x:v>`f"₹{price}"`</x:v>
       </x:c>
       <x:c r="N26" t="str">
-        <x:v>`path = "C:\new\table"`</x:v>
+        <x:v>`f"₹{price:2}"`</x:v>
       </x:c>
       <x:c r="O26" t="str">
-        <x:v>`path = f"C:\new\table"`</x:v>
+        <x:v>`f"₹{price:.1f}"`</x:v>
       </x:c>
       <x:c r="P26" t="str">
-        <x:v>`path = "C:/n/t"`</x:v>
+        <x:v>`f"₹{price:.2f}"`</x:v>
       </x:c>
       <x:c r="Q26" t="n">
-        <x:v>1</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="27" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A27" t="str">
-        <x:v>Python - MCQ - 5.2.16</x:v>
+        <x:v>Python - MCQ - 5.3.6</x:v>
       </x:c>
       <x:c r="B27" t="str">
-        <x:v>A policy notice spans several lines and should remain readable in the Python source.
-A four-line notice must remain readable in the source and preserve its typed line breaks. Choose the most appropriate representation.</x:v>
+        <x:v>Making a large order total readable
+A wholesale order total is `1500000`. Which f-string displays it as `1,500,000`?</x:v>
       </x:c>
       <x:c r="C27" t="str">
-        <x:v>Triple quotes naturally preserve multiple physical lines and blank lines.</x:v>
+        <x:v>The comma format specifier inserts thousands separators.</x:v>
       </x:c>
       <x:c r="D27" t="n">
         <x:v>8</x:v>
@@ -1813,10 +1822,10 @@
         <x:v>medium</x:v>
       </x:c>
       <x:c r="G27" t="str">
-        <x:v>evaluate</x:v>
+        <x:v>apply</x:v>
       </x:c>
       <x:c r="H27" t="str">
-        <x:v>python - Set 2</x:v>
+        <x:v>python - Set 3</x:v>
       </x:c>
       <x:c r="I27" t="str">
         <x:v>python</x:v>
@@ -1825,50 +1834,54 @@
         <x:v>strings</x:v>
       </x:c>
       <x:c r="K27" t="str">
-        <x:v>escape-sequences</x:v>
+        <x:v>string-formatting</x:v>
       </x:c>
       <x:c r="L27"/>
       <x:c r="M27" t="str">
-        <x:v>Four unrelated variables with one word each</x:v>
+        <x:v>`f"{total:.2f}"`</x:v>
       </x:c>
       <x:c r="N27" t="str">
-        <x:v>A standard quoted string broken across physical lines without escapes</x:v>
+        <x:v>`f"{total:,}"`</x:v>
       </x:c>
       <x:c r="O27" t="str">
-        <x:v>A triple-quoted string containing the four lines</x:v>
+        <x:v>`f"{total:.1%}"`</x:v>
       </x:c>
       <x:c r="P27" t="str">
-        <x:v>An integer converted to text</x:v>
+        <x:v>`f"{total:^10}"`</x:v>
       </x:c>
       <x:c r="Q27" t="n">
-        <x:v>3</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="28" ht="39.599998474121094" hidden="0" customHeight="1">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A28" t="str">
-        <x:v>Python - MCQ - 5.2.17</x:v>
+        <x:v>Python - MCQ - 5.3.7</x:v>
       </x:c>
       <x:c r="B28" t="str">
-        <x:v>A customer testimonial includes quotation marks that must appear inside a double-quoted literal.
-The outer delimiter must remain double quotes. Select the valid string for `She said "yes"`.</x:v>
+        <x:v>Repairing a percentage that is scaled twice
+A dashboard stores `completion = 0.873` but incorrectly multiplies it before applying percentage formatting:
+```python
+display = f"{completion * 100:.1%}"
+```
+The screen shows `8730.0%` instead of `87.3%`. Which smallest repair removes the double scaling?</x:v>
       </x:c>
       <x:c r="C28" t="str">
-        <x:v>Backslash-escaped double quotes are treated as content instead of delimiters.</x:v>
+        <x:v>`.1%` scales the proportion and displays one decimal place plus a percent sign.</x:v>
       </x:c>
       <x:c r="D28" t="n">
-        <x:v>5</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="E28" t="str">
         <x:v>published</x:v>
       </x:c>
       <x:c r="F28" t="str">
-        <x:v>easy</x:v>
+        <x:v>medium</x:v>
       </x:c>
       <x:c r="G28" t="str">
-        <x:v>analyze</x:v>
+        <x:v>evaluate</x:v>
       </x:c>
       <x:c r="H28" t="str">
-        <x:v>python - Set 2</x:v>
+        <x:v>python - Set 3</x:v>
       </x:c>
       <x:c r="I28" t="str">
         <x:v>python</x:v>
@@ -1877,39 +1890,35 @@
         <x:v>strings</x:v>
       </x:c>
       <x:c r="K28" t="str">
-        <x:v>escape-sequences</x:v>
+        <x:v>string-formatting</x:v>
       </x:c>
       <x:c r="L28"/>
       <x:c r="M28" t="str">
-        <x:v>`text = "She said "yes""`</x:v>
+        <x:v>`f"{completion:.1f}%"`</x:v>
       </x:c>
       <x:c r="N28" t="str">
-        <x:v>`text = "She said \"yes\""`</x:v>
+        <x:v>`f"{completion * 100:.1%}"`</x:v>
       </x:c>
       <x:c r="O28" t="str">
-        <x:v>`text = She said "yes"`</x:v>
+        <x:v>`f"{completion:.1%}"`</x:v>
       </x:c>
       <x:c r="P28" t="str">
-        <x:v>`text = "She said /"yes/""`</x:v>
+        <x:v>`f"{completion:,.1f}"`</x:v>
       </x:c>
       <x:c r="Q28" t="n">
-        <x:v>2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="29" ht="105.5999984741211" hidden="0" customHeight="1">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A29" t="str">
-        <x:v>Python - MCQ - 5.2.18</x:v>
+        <x:v>Python - MCQ - 5.3.8</x:v>
       </x:c>
       <x:c r="B29" t="str">
-        <x:v>A social-media caption contains both a line break and an embedded quoted phrase.
-```python
-caption = "New
-"Craft" collection"
-```
-The intended value contains a newline followed by `"Craft" collection`. Approve the complete one-line repair.</x:v>
+        <x:v>Aligning a product name and its price
+A price list requires the product name left-aligned in a width of 12 and its price right-aligned in a width of 8. Which template applies those two alignments?</x:v>
       </x:c>
       <x:c r="C29" t="str">
-        <x:v>The physical newline becomes `\n`, and both embedded double quotes are escaped.</x:v>
+        <x:v>`&lt;12` left-aligns the name, while `&gt;8.2f` right-aligns a two-decimal price.</x:v>
       </x:c>
       <x:c r="D29" t="n">
         <x:v>10</x:v>
@@ -1921,10 +1930,10 @@
         <x:v>hard</x:v>
       </x:c>
       <x:c r="G29" t="str">
-        <x:v>evaluate</x:v>
+        <x:v>apply</x:v>
       </x:c>
       <x:c r="H29" t="str">
-        <x:v>python - Set 2</x:v>
+        <x:v>python - Set 3</x:v>
       </x:c>
       <x:c r="I29" t="str">
         <x:v>python</x:v>
@@ -1933,54 +1942,50 @@
         <x:v>strings</x:v>
       </x:c>
       <x:c r="K29" t="str">
-        <x:v>escape-sequences</x:v>
+        <x:v>string-formatting</x:v>
       </x:c>
       <x:c r="L29"/>
       <x:c r="M29" t="str">
-        <x:v>`caption = "New/nCraft collection"`</x:v>
+        <x:v>`f"{name:&lt;12}{price:&gt;8.2f}"`</x:v>
       </x:c>
       <x:c r="N29" t="str">
-        <x:v>`caption = "New"\n"Craft collection"`</x:v>
+        <x:v>`f"{name:&gt;12}{price:&lt;8.2f}"`</x:v>
       </x:c>
       <x:c r="O29" t="str">
-        <x:v>`caption = 'New\n'Craft' collection'`</x:v>
+        <x:v>`f"{name:^12}{price:^8.2f}"`</x:v>
       </x:c>
       <x:c r="P29" t="str">
-        <x:v>`caption = "New\n\"Craft\" collection"`</x:v>
+        <x:v>`f"{name:12.2f}{price:8}"`</x:v>
       </x:c>
       <x:c r="Q29" t="n">
-        <x:v>4</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="30" ht="92.4000015258789" hidden="0" customHeight="1">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A30" t="str">
-        <x:v>Python - MCQ - 5.2.19</x:v>
+        <x:v>Python - MCQ - 5.3.9</x:v>
       </x:c>
       <x:c r="B30" t="str">
-        <x:v>A giveaway organiser cleans punctuation and capitalisation before counting the words in an entry.
-```python
-raw = "  Python, python, CRAFT  "
-clean = raw.strip().lower().replace(",", "")
-word_count = len(clean.split())
-```</x:v>
+        <x:v>Placing the order total on a new line
+A receipt needs `Item: Notebook` on the first line and `Total: 80` on the second. Which escape sequence creates that line break inside one string?</x:v>
       </x:c>
       <x:c r="C30" t="str">
-        <x:v>Cleaning produces `"python python craft"`, which splits into three words.</x:v>
+        <x:v>`\n` inserts a newline within a string.</x:v>
       </x:c>
       <x:c r="D30" t="n">
-        <x:v>8</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E30" t="str">
         <x:v>published</x:v>
       </x:c>
       <x:c r="F30" t="str">
-        <x:v>medium</x:v>
+        <x:v>easy</x:v>
       </x:c>
       <x:c r="G30" t="str">
-        <x:v>evaluate</x:v>
+        <x:v>apply</x:v>
       </x:c>
       <x:c r="H30" t="str">
-        <x:v>python - Set 2</x:v>
+        <x:v>python - Set 3</x:v>
       </x:c>
       <x:c r="I30" t="str">
         <x:v>python</x:v>
@@ -1989,267 +1994,251 @@
         <x:v>strings</x:v>
       </x:c>
       <x:c r="K30" t="str">
-        <x:v>text-processing</x:v>
+        <x:v>escape-sequences</x:v>
       </x:c>
       <x:c r="L30"/>
       <x:c r="M30" t="str">
-        <x:v>`2`</x:v>
+        <x:v>`\t`</x:v>
       </x:c>
       <x:c r="N30" t="str">
-        <x:v>`4`</x:v>
+        <x:v>`\n`</x:v>
       </x:c>
       <x:c r="O30" t="str">
-        <x:v>`3`</x:v>
+        <x:v>`\\`</x:v>
       </x:c>
       <x:c r="P30" t="str">
-        <x:v>`22`</x:v>
+        <x:v>`\"`</x:v>
       </x:c>
       <x:c r="Q30" t="n">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" ht="39.599998474121094" hidden="0" customHeight="1">
+      <x:c r="A31" t="str">
+        <x:v>Python - MCQ - 5.3.10</x:v>
+      </x:c>
+      <x:c r="B31" t="str">
+        <x:v>Preserving quotation marks in a review
+A message must contain the exact text `She said "great"` while using double quotes around the Python string. Which assignment is valid?</x:v>
+      </x:c>
+      <x:c r="C31" t="str">
+        <x:v>Escaped double quotes remain part of the text rather than terminating the string.</x:v>
+      </x:c>
+      <x:c r="D31" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="E31" t="str">
+        <x:v>published</x:v>
+      </x:c>
+      <x:c r="F31" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="G31" t="str">
+        <x:v>evaluate</x:v>
+      </x:c>
+      <x:c r="H31" t="str">
+        <x:v>python - Set 3</x:v>
+      </x:c>
+      <x:c r="I31" t="str">
+        <x:v>python</x:v>
+      </x:c>
+      <x:c r="J31" t="str">
+        <x:v>strings</x:v>
+      </x:c>
+      <x:c r="K31" t="str">
+        <x:v>escape-sequences</x:v>
+      </x:c>
+      <x:c r="L31"/>
+      <x:c r="M31" t="str">
+        <x:v>`review = "She said "great""`</x:v>
+      </x:c>
+      <x:c r="N31" t="str">
+        <x:v>`review = "She said \great\"`</x:v>
+      </x:c>
+      <x:c r="O31" t="str">
+        <x:v>`review = "She said \"great\""`</x:v>
+      </x:c>
+      <x:c r="P31" t="str">
+        <x:v>`review = "She said /"great/""`</x:v>
+      </x:c>
+      <x:c r="Q31" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>
-    <x:row r="31" ht="105.5999984741211" hidden="0" customHeight="1">
-      <x:c r="A31" t="str">
-        <x:v>Python - MCQ - 5.2.20</x:v>
-      </x:c>
-      <x:c r="B31" t="str">
-        <x:v>A structured-entry importer expects three comma-separated fields but receives only two.
+    <x:row r="32" ht="39.599998474121094" hidden="0" customHeight="1">
+      <x:c r="A32" t="str">
+        <x:v>Python - MCQ - 5.4.1</x:v>
+      </x:c>
+      <x:c r="B32" t="str">
+        <x:v>A Windows path must keep its backslashes
+A configuration value must preserve the characters in `C:\new\table` rather than interpreting `\n` and `\t`. Which literal is clearest for that purpose?</x:v>
+      </x:c>
+      <x:c r="C32" t="str">
+        <x:v>The raw-string prefix treats backslashes literally, preventing newline and tab escapes.</x:v>
+      </x:c>
+      <x:c r="D32" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="E32" t="str">
+        <x:v>published</x:v>
+      </x:c>
+      <x:c r="F32" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="G32" t="str">
+        <x:v>evaluate</x:v>
+      </x:c>
+      <x:c r="H32" t="str">
+        <x:v>python - Set 4</x:v>
+      </x:c>
+      <x:c r="I32" t="str">
+        <x:v>python</x:v>
+      </x:c>
+      <x:c r="J32" t="str">
+        <x:v>strings</x:v>
+      </x:c>
+      <x:c r="K32" t="str">
+        <x:v>escape-sequences</x:v>
+      </x:c>
+      <x:c r="L32"/>
+      <x:c r="M32" t="str">
+        <x:v>`path = r"C:\new\table"`</x:v>
+      </x:c>
+      <x:c r="N32" t="str">
+        <x:v>`path = "C:\new\table"`</x:v>
+      </x:c>
+      <x:c r="O32" t="str">
+        <x:v>`path = "C:/n/e/w/t/a/b/l/e"`</x:v>
+      </x:c>
+      <x:c r="P32" t="str">
+        <x:v>`path = "C:newtable"`</x:v>
+      </x:c>
+      <x:c r="Q32" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" ht="39.599998474121094" hidden="0" customHeight="1">
+      <x:c r="A33" t="str">
+        <x:v>Python - MCQ - 5.4.2</x:v>
+      </x:c>
+      <x:c r="B33" t="str">
+        <x:v>Keeping a three-line message readable in source code
+A confirmation email has three fixed lines and should be written in source with the same visible line structure. Which representation best fits?</x:v>
+      </x:c>
+      <x:c r="C33" t="str">
+        <x:v>Triple quotes preserve a multi-line block in the same visible layout used in the source.</x:v>
+      </x:c>
+      <x:c r="D33" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E33" t="str">
+        <x:v>published</x:v>
+      </x:c>
+      <x:c r="F33" t="str">
+        <x:v>hard</x:v>
+      </x:c>
+      <x:c r="G33" t="str">
+        <x:v>evaluate</x:v>
+      </x:c>
+      <x:c r="H33" t="str">
+        <x:v>python - Set 4</x:v>
+      </x:c>
+      <x:c r="I33" t="str">
+        <x:v>python</x:v>
+      </x:c>
+      <x:c r="J33" t="str">
+        <x:v>strings</x:v>
+      </x:c>
+      <x:c r="K33" t="str">
+        <x:v>escape-sequences</x:v>
+      </x:c>
+      <x:c r="L33"/>
+      <x:c r="M33" t="str">
+        <x:v>A one-line string with every space replaced by a tab</x:v>
+      </x:c>
+      <x:c r="N33" t="str">
+        <x:v>Three unrelated variables that are never combined</x:v>
+      </x:c>
+      <x:c r="O33" t="str">
+        <x:v>A raw string with no actual line breaks</x:v>
+      </x:c>
+      <x:c r="P33" t="str">
+        <x:v>A triple-quoted string containing the three lines</x:v>
+      </x:c>
+      <x:c r="Q33" t="n">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" ht="118.80000305175781" hidden="0" customHeight="1">
+      <x:c r="A34" t="str">
+        <x:v>Python - MCQ - 5.4.3</x:v>
+      </x:c>
+      <x:c r="B34" t="str">
+        <x:v>Cleaning a caption through a method pipeline
+A caption arrives as `"  Hello, WORLD  "`. The pipeline is:
 ```python
-line = "Asha,19"
+clean = caption.strip().lower().replace(",", "")
+```
+Which cleaned caption is stored?</x:v>
+      </x:c>
+      <x:c r="C34" t="str">
+        <x:v>The chain trims the ends, lowercases the letters, and removes the comma.</x:v>
+      </x:c>
+      <x:c r="D34" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="E34" t="str">
+        <x:v>published</x:v>
+      </x:c>
+      <x:c r="F34" t="str">
+        <x:v>easy</x:v>
+      </x:c>
+      <x:c r="G34" t="str">
+        <x:v>apply</x:v>
+      </x:c>
+      <x:c r="H34" t="str">
+        <x:v>python - Set 4</x:v>
+      </x:c>
+      <x:c r="I34" t="str">
+        <x:v>python</x:v>
+      </x:c>
+      <x:c r="J34" t="str">
+        <x:v>strings</x:v>
+      </x:c>
+      <x:c r="K34" t="str">
+        <x:v>text-processing</x:v>
+      </x:c>
+      <x:c r="L34"/>
+      <x:c r="M34" t="str">
+        <x:v>`"Hello WORLD"`</x:v>
+      </x:c>
+      <x:c r="N34" t="str">
+        <x:v>`"  hello world  "`</x:v>
+      </x:c>
+      <x:c r="O34" t="str">
+        <x:v>`"hello world"`</x:v>
+      </x:c>
+      <x:c r="P34" t="str">
+        <x:v>`"hello, world"`</x:v>
+      </x:c>
+      <x:c r="Q34" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" ht="118.80000305175781" hidden="0" customHeight="1">
+      <x:c r="A35" t="str">
+        <x:v>Python - MCQ - 5.4.4</x:v>
+      </x:c>
+      <x:c r="B35" t="str">
+        <x:v>Unpacking a structured customer record
+A line contains `"Asha,20,Pune"` and is processed with:
+```python
 name, age, city = line.split(",")
 ```
-Select the correct review finding.</x:v>
-      </x:c>
-      <x:c r="C31" t="str">
-        <x:v>The number of produced pieces must match the number of target variables during unpacking.</x:v>
-      </x:c>
-      <x:c r="D31" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="E31" t="str">
-        <x:v>published</x:v>
-      </x:c>
-      <x:c r="F31" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="G31" t="str">
-        <x:v>evaluate</x:v>
-      </x:c>
-      <x:c r="H31" t="str">
-        <x:v>python - Set 2</x:v>
-      </x:c>
-      <x:c r="I31" t="str">
-        <x:v>python</x:v>
-      </x:c>
-      <x:c r="J31" t="str">
-        <x:v>strings</x:v>
-      </x:c>
-      <x:c r="K31" t="str">
-        <x:v>text-processing</x:v>
-      </x:c>
-      <x:c r="L31"/>
-      <x:c r="M31" t="str">
-        <x:v>Splitting returns two pieces, so unpacking into three variables raises an error.</x:v>
-      </x:c>
-      <x:c r="N31" t="str">
-        <x:v>`city` automatically becomes an empty string.</x:v>
-      </x:c>
-      <x:c r="O31" t="str">
-        <x:v>`age` and `city` both become `"19"`.</x:v>
-      </x:c>
-      <x:c r="P31" t="str">
-        <x:v>`split()` refuses comma separators.</x:v>
-      </x:c>
-      <x:c r="Q31" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="32" ht="79.19999694824219" hidden="0" customHeight="1">
-      <x:c r="A32" t="str">
-        <x:v>Python - MCQ - 5.2.21</x:v>
-      </x:c>
-      <x:c r="B32" t="str">
-        <x:v>A content dashboard reports character count after excluding ordinary spaces.
-```python
-sentence = "red clay art"
-characters_without_spaces = __________
-```</x:v>
-      </x:c>
-      <x:c r="C32" t="str">
-        <x:v>Removing spaces creates the text to be measured; `len()` then counts its remaining characters.</x:v>
-      </x:c>
-      <x:c r="D32" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="E32" t="str">
-        <x:v>published</x:v>
-      </x:c>
-      <x:c r="F32" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="G32" t="str">
-        <x:v>analyze</x:v>
-      </x:c>
-      <x:c r="H32" t="str">
-        <x:v>python - Set 2</x:v>
-      </x:c>
-      <x:c r="I32" t="str">
-        <x:v>python</x:v>
-      </x:c>
-      <x:c r="J32" t="str">
-        <x:v>strings</x:v>
-      </x:c>
-      <x:c r="K32" t="str">
-        <x:v>text-processing</x:v>
-      </x:c>
-      <x:c r="L32"/>
-      <x:c r="M32" t="str">
-        <x:v>`sentence.count(" ")`</x:v>
-      </x:c>
-      <x:c r="N32" t="str">
-        <x:v>`len(sentence.replace(" ", ""))`</x:v>
-      </x:c>
-      <x:c r="O32" t="str">
-        <x:v>`len(sentence.split(" "))`</x:v>
-      </x:c>
-      <x:c r="P32" t="str">
-        <x:v>`sentence.find(" ")`</x:v>
-      </x:c>
-      <x:c r="Q32" t="n">
-        <x:v>2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="33" ht="171.60000610351562" hidden="0" customHeight="1">
-      <x:c r="A33" t="str">
-        <x:v>Python - MCQ - 5.2.22</x:v>
-      </x:c>
-      <x:c r="B33" t="str">
-        <x:v>A cleanup team is checking whether trimming before replacement behaves the same as replacing before trimming.
-For `text = "  tea  "`, compare:
-```python
-# Version A
-text.strip().replace(" ", "-")
-# Version B
-text.replace(" ", "-").strip()
-```
-Select the accurate result pair.</x:v>
-      </x:c>
-      <x:c r="C33" t="str">
-        <x:v>Version A removes edge spaces before replacement; Version B turns them into hyphens, which `strip()` does not remove.</x:v>
-      </x:c>
-      <x:c r="D33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="E33" t="str">
-        <x:v>published</x:v>
-      </x:c>
-      <x:c r="F33" t="str">
-        <x:v>hard</x:v>
-      </x:c>
-      <x:c r="G33" t="str">
-        <x:v>evaluate</x:v>
-      </x:c>
-      <x:c r="H33" t="str">
-        <x:v>python - Set 2</x:v>
-      </x:c>
-      <x:c r="I33" t="str">
-        <x:v>python</x:v>
-      </x:c>
-      <x:c r="J33" t="str">
-        <x:v>strings</x:v>
-      </x:c>
-      <x:c r="K33" t="str">
-        <x:v>string-methods</x:v>
-      </x:c>
-      <x:c r="L33"/>
-      <x:c r="M33" t="str">
-        <x:v>Both produce `"tea"`.</x:v>
-      </x:c>
-      <x:c r="N33" t="str">
-        <x:v>A produces `"--tea--"`; B produces `"tea"`.</x:v>
-      </x:c>
-      <x:c r="O33" t="str">
-        <x:v>Both produce `"--tea--"`.</x:v>
-      </x:c>
-      <x:c r="P33" t="str">
-        <x:v>A produces `"tea"`; B produces `"--tea--"`.</x:v>
-      </x:c>
-      <x:c r="Q33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="34" ht="79.19999694824219" hidden="0" customHeight="1">
-      <x:c r="A34" t="str">
-        <x:v>Python - MCQ - 5.2.23</x:v>
-      </x:c>
-      <x:c r="B34" t="str">
-        <x:v>A content-moderation search must find a keyword regardless of how users capitalise it.
-```python
-sentence = "Learn PYTHON Today"
-contains_python = __________
-```</x:v>
-      </x:c>
-      <x:c r="C34" t="str">
-        <x:v>Lowercasing the searchable text makes membership independent of the original capitalisation.</x:v>
-      </x:c>
-      <x:c r="D34" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="E34" t="str">
-        <x:v>published</x:v>
-      </x:c>
-      <x:c r="F34" t="str">
-        <x:v>easy</x:v>
-      </x:c>
-      <x:c r="G34" t="str">
-        <x:v>understand</x:v>
-      </x:c>
-      <x:c r="H34" t="str">
-        <x:v>python - Set 2</x:v>
-      </x:c>
-      <x:c r="I34" t="str">
-        <x:v>python</x:v>
-      </x:c>
-      <x:c r="J34" t="str">
-        <x:v>strings</x:v>
-      </x:c>
-      <x:c r="K34" t="str">
-        <x:v>searching-and-membership</x:v>
-      </x:c>
-      <x:c r="L34"/>
-      <x:c r="M34" t="str">
-        <x:v>`"python" in sentence.lower()`</x:v>
-      </x:c>
-      <x:c r="N34" t="str">
-        <x:v>`"python" == sentence`</x:v>
-      </x:c>
-      <x:c r="O34" t="str">
-        <x:v>`sentence.find("PYTHON") == -1`</x:v>
-      </x:c>
-      <x:c r="P34" t="str">
-        <x:v>`sentence.count("python") == 0`</x:v>
-      </x:c>
-      <x:c r="Q34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="35" ht="158.39999389648438" hidden="0" customHeight="1">
-      <x:c r="A35" t="str">
-        <x:v>Python - MCQ - 5.2.24</x:v>
-      </x:c>
-      <x:c r="B35" t="str">
-        <x:v>A keyword appears at the very beginning of a caption, but the search condition mistakenly reports failure.
-```python
-text = "craft sale"
-if text.find("craft"):
-    status = "Found"
-else:
-    status = "Missing"
-```
-The word exists at the beginning. Why is `status` still `"Missing"`?</x:v>
+Which city value reaches the customer profile?</x:v>
       </x:c>
       <x:c r="C35" t="str">
-        <x:v>Zero is a valid position but a falsy condition value, so the sentinel must be tested explicitly.</x:v>
+        <x:v>Splitting yields `"Asha"`, `"20"`, and `"Pune"` in that order.</x:v>
       </x:c>
       <x:c r="D35" t="n">
         <x:v>8</x:v>
@@ -2264,7 +2253,7 @@
         <x:v>analyze</x:v>
       </x:c>
       <x:c r="H35" t="str">
-        <x:v>python - Set 2</x:v>
+        <x:v>python - Set 4</x:v>
       </x:c>
       <x:c r="I35" t="str">
         <x:v>python</x:v>
@@ -2273,40 +2262,35 @@
         <x:v>strings</x:v>
       </x:c>
       <x:c r="K35" t="str">
-        <x:v>searching-and-membership</x:v>
+        <x:v>text-processing</x:v>
       </x:c>
       <x:c r="L35"/>
       <x:c r="M35" t="str">
-        <x:v>`find()` is case-insensitive.</x:v>
+        <x:v>`"Pune"`</x:v>
       </x:c>
       <x:c r="N35" t="str">
-        <x:v>`find()` returns `-1` for a match.</x:v>
+        <x:v>`"20"`</x:v>
       </x:c>
       <x:c r="O35" t="str">
-        <x:v>`find()` returns index `0`, which is falsy; compare the result with `-1` instead.</x:v>
+        <x:v>`"Asha,20"`</x:v>
       </x:c>
       <x:c r="P35" t="str">
-        <x:v>`find()` works only on one-character searches.</x:v>
+        <x:v>`"Asha"`</x:v>
       </x:c>
       <x:c r="Q35" t="n">
-        <x:v>3</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="36" ht="132" hidden="0" customHeight="1">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A36" t="str">
-        <x:v>Python - MCQ - 5.2.25</x:v>
+        <x:v>Python - MCQ - 5.4.5</x:v>
       </x:c>
       <x:c r="B36" t="str">
-        <x:v>A message checker inspects the final character even when the user may submit an empty string.
-```python
-text = input("Text: ")
-if text[-1] == ".":
-    status = "Sentence"
-```
-What is the smallest safe structural repair?</x:v>
+        <x:v>Counting words despite irregular spacing
+A feedback message is `"fast   delivery and packaging"`. The analyzer uses `len(message.split())`. Which word count is reported?</x:v>
       </x:c>
       <x:c r="C36" t="str">
-        <x:v>Empty input has no last character; a truthiness guard prevents out-of-range indexing.</x:v>
+        <x:v>Default splitting yields the four words fast, delivery, and, and packaging.</x:v>
       </x:c>
       <x:c r="D36" t="n">
         <x:v>8</x:v>
@@ -2318,10 +2302,10 @@
         <x:v>medium</x:v>
       </x:c>
       <x:c r="G36" t="str">
-        <x:v>analyze</x:v>
+        <x:v>apply</x:v>
       </x:c>
       <x:c r="H36" t="str">
-        <x:v>python - Set 2</x:v>
+        <x:v>python - Set 4</x:v>
       </x:c>
       <x:c r="I36" t="str">
         <x:v>python</x:v>
@@ -2330,50 +2314,54 @@
         <x:v>strings</x:v>
       </x:c>
       <x:c r="K36" t="str">
-        <x:v>indexing-and-slicing</x:v>
+        <x:v>text-processing</x:v>
       </x:c>
       <x:c r="L36"/>
       <x:c r="M36" t="str">
-        <x:v>Use `text[0]` instead.</x:v>
+        <x:v>`6`</x:v>
       </x:c>
       <x:c r="N36" t="str">
-        <x:v>Replace `-1` with `1`.</x:v>
+        <x:v>`3`</x:v>
       </x:c>
       <x:c r="O36" t="str">
-        <x:v>Convert `text` to an integer first.</x:v>
+        <x:v>`5`</x:v>
       </x:c>
       <x:c r="P36" t="str">
-        <x:v>Check that `text` is non-empty before evaluating `text[-1]`.</x:v>
+        <x:v>`4`</x:v>
       </x:c>
       <x:c r="Q36" t="n">
         <x:v>4</x:v>
       </x:c>
     </x:row>
-    <x:row r="37" ht="39.599998474121094" hidden="0" customHeight="1">
+    <x:row r="37" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A37" t="str">
-        <x:v>Python - MCQ - 5.2.26</x:v>
+        <x:v>Python - MCQ - 5.4.6</x:v>
       </x:c>
       <x:c r="B37" t="str">
-        <x:v>A product preview should return up to five characters without failing on shorter names.
-A preview should return up to the first five characters, even when the source contains fewer than five. Choose the safest expression.</x:v>
+        <x:v>Counting characters but excluding spaces
+An analyzer measures `"data science"` after removing ordinary spaces:
+```python
+character_count = len(text.replace(" ", ""))
+```
+Which count reaches the report?</x:v>
       </x:c>
       <x:c r="C37" t="str">
-        <x:v>Slicing safely returns the available prefix without requiring five characters to exist.</x:v>
+        <x:v>The four letters in data plus seven in science give 11 after the space is removed.</x:v>
       </x:c>
       <x:c r="D37" t="n">
-        <x:v>5</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E37" t="str">
         <x:v>published</x:v>
       </x:c>
       <x:c r="F37" t="str">
-        <x:v>easy</x:v>
+        <x:v>hard</x:v>
       </x:c>
       <x:c r="G37" t="str">
-        <x:v>evaluate</x:v>
+        <x:v>apply</x:v>
       </x:c>
       <x:c r="H37" t="str">
-        <x:v>python - Set 2</x:v>
+        <x:v>python - Set 4</x:v>
       </x:c>
       <x:c r="I37" t="str">
         <x:v>python</x:v>
@@ -2382,40 +2370,35 @@
         <x:v>strings</x:v>
       </x:c>
       <x:c r="K37" t="str">
-        <x:v>indexing-and-slicing</x:v>
+        <x:v>text-processing</x:v>
       </x:c>
       <x:c r="L37"/>
       <x:c r="M37" t="str">
-        <x:v>`text[5]`</x:v>
+        <x:v>`12`</x:v>
       </x:c>
       <x:c r="N37" t="str">
-        <x:v>`text[:5]`</x:v>
+        <x:v>`11`</x:v>
       </x:c>
       <x:c r="O37" t="str">
-        <x:v>`text[-5]`</x:v>
+        <x:v>`10`</x:v>
       </x:c>
       <x:c r="P37" t="str">
-        <x:v>`text[0] + text[1] + text[2] + text[3] + text[4]`</x:v>
+        <x:v>`2`</x:v>
       </x:c>
       <x:c r="Q37" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
-    <x:row r="38" ht="132" hidden="0" customHeight="1">
+    <x:row r="38" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A38" t="str">
-        <x:v>Python - MCQ - 5.2.27</x:v>
+        <x:v>Python - MCQ - 5.4.7</x:v>
       </x:c>
       <x:c r="B38" t="str">
-        <x:v>A marketing tool converts a multi-word craft phrase into one title-cased hashtag with no spaces.
-```python
-phrase = "handmade clay art"
-words = phrase.title().split()
-hashtag = "#" + __________
-```
-The required result is `#HandmadeClayArt`.</x:v>
+        <x:v>Finding a keyword without caring about case
+A moderator searches for a user-supplied `keyword` inside `message`, and capitalisation should not affect the result. Which condition normalises both sides?</x:v>
       </x:c>
       <x:c r="C38" t="str">
-        <x:v>Joining with the empty string fuses the transformed words without separators.</x:v>
+        <x:v>Lowercasing both strings makes the containment test case-insensitive.</x:v>
       </x:c>
       <x:c r="D38" t="n">
         <x:v>8</x:v>
@@ -2427,10 +2410,10 @@
         <x:v>medium</x:v>
       </x:c>
       <x:c r="G38" t="str">
-        <x:v>apply</x:v>
+        <x:v>evaluate</x:v>
       </x:c>
       <x:c r="H38" t="str">
-        <x:v>python - Set 2</x:v>
+        <x:v>python - Set 4</x:v>
       </x:c>
       <x:c r="I38" t="str">
         <x:v>python</x:v>
@@ -2439,39 +2422,40 @@
         <x:v>strings</x:v>
       </x:c>
       <x:c r="K38" t="str">
-        <x:v>split-and-join</x:v>
+        <x:v>text-processing</x:v>
       </x:c>
       <x:c r="L38"/>
       <x:c r="M38" t="str">
-        <x:v>`" ".join(words)`</x:v>
+        <x:v>`keyword.lower() in message.lower()`</x:v>
       </x:c>
       <x:c r="N38" t="str">
-        <x:v>`",".join(words)`</x:v>
+        <x:v>`keyword in message.lower()`</x:v>
       </x:c>
       <x:c r="O38" t="str">
-        <x:v>`"".join(words)`</x:v>
+        <x:v>`keyword.upper() == message.lower()`</x:v>
       </x:c>
       <x:c r="P38" t="str">
-        <x:v>`words.split()`</x:v>
+        <x:v>`message.find(keyword) == 0`</x:v>
       </x:c>
       <x:c r="Q38" t="n">
-        <x:v>3</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="39" ht="105.5999984741211" hidden="0" customHeight="1">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" ht="132" hidden="0" customHeight="1">
       <x:c r="A39" t="str">
-        <x:v>Python - MCQ - 5.2.28</x:v>
+        <x:v>Python - MCQ - 5.4.8</x:v>
       </x:c>
       <x:c r="B39" t="str">
-        <x:v>A user-profile service stores both the original display name and a separate uppercase version.
+        <x:v>Converting messy tags into a clean slug
+A tag line is `" red,BLUE, green "`. The program runs:
 ```python
-original = "Meera"
-upper_name = original.upper()
+parts = tag_line.replace(" ", "").lower().split(",")
+slug = "-".join(parts)
 ```
-Complete the final state pair.</x:v>
+Which slug is produced?</x:v>
       </x:c>
       <x:c r="C39" t="str">
-        <x:v>The method returns a new uppercase string while leaving the original immutable value unchanged.</x:v>
+        <x:v>The pipeline removes spaces, normalises case, splits on commas, and rejoins with hyphens.</x:v>
       </x:c>
       <x:c r="D39" t="n">
         <x:v>8</x:v>
@@ -2486,7 +2470,7 @@
         <x:v>apply</x:v>
       </x:c>
       <x:c r="H39" t="str">
-        <x:v>python - Set 2</x:v>
+        <x:v>python - Set 4</x:v>
       </x:c>
       <x:c r="I39" t="str">
         <x:v>python</x:v>
@@ -2495,54 +2479,54 @@
         <x:v>strings</x:v>
       </x:c>
       <x:c r="K39" t="str">
-        <x:v>string-methods</x:v>
+        <x:v>text-processing</x:v>
       </x:c>
       <x:c r="L39"/>
       <x:c r="M39" t="str">
-        <x:v>`original == "Meera"`; `upper_name == "MEERA"`</x:v>
+        <x:v>`"redbluegreen"`</x:v>
       </x:c>
       <x:c r="N39" t="str">
-        <x:v>Both variables contain `"MEERA"`.</x:v>
+        <x:v>`"red,blue,green"`</x:v>
       </x:c>
       <x:c r="O39" t="str">
-        <x:v>Both variables contain `"Meera"`.</x:v>
+        <x:v>`"red-blue-green"`</x:v>
       </x:c>
       <x:c r="P39" t="str">
-        <x:v>`original` becomes empty after the method call.</x:v>
+        <x:v>`" Red-Blue-Green "`</x:v>
       </x:c>
       <x:c r="Q39" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="40" ht="105.5999984741211" hidden="0" customHeight="1">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A40" t="str">
-        <x:v>Python - MCQ - 5.2.29</x:v>
+        <x:v>Python - MCQ - 5.4.9</x:v>
       </x:c>
       <x:c r="B40" t="str">
-        <x:v>A signup form uses only an at-sign check and a `.com` suffix as rough email validation.
+        <x:v>An extra comma changes the record shape
+An importer expects exactly three fields:
 ```python
-email = input("Email: ").strip().lower()
-valid = "@" in email and email.endswith(".com")
+name, age, city = line.split(",")
 ```
-Which input proves that this is only a rough check rather than complete email validation?</x:v>
+The line is `"Asha,20,Pune,India"`, and the importer rejects it. Which support note identifies the structural mismatch?</x:v>
       </x:c>
       <x:c r="C40" t="str">
-        <x:v>`"@.com"` satisfies both simple checks despite lacking meaningful text around the at sign.</x:v>
+        <x:v>The three commas create four pieces, which cannot be unpacked into only three variables.</x:v>
       </x:c>
       <x:c r="D40" t="n">
-        <x:v>10</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="E40" t="str">
         <x:v>published</x:v>
       </x:c>
       <x:c r="F40" t="str">
-        <x:v>hard</x:v>
+        <x:v>medium</x:v>
       </x:c>
       <x:c r="G40" t="str">
         <x:v>analyze</x:v>
       </x:c>
       <x:c r="H40" t="str">
-        <x:v>python - Set 2</x:v>
+        <x:v>python - Set 4</x:v>
       </x:c>
       <x:c r="I40" t="str">
         <x:v>python</x:v>
@@ -2555,46 +2539,54 @@
       </x:c>
       <x:c r="L40"/>
       <x:c r="M40" t="str">
-        <x:v>`"asha@example.com"`</x:v>
+        <x:v>Adding `maxsplit=2` proves the original line has only three fields because the last value would automatically remain just `"Pune"`</x:v>
       </x:c>
       <x:c r="N40" t="str">
-        <x:v>`"  ASHA@EXAMPLE.COM  "`</x:v>
+        <x:v>The split creates four pieces, but the assignment provides only three variables</x:v>
       </x:c>
       <x:c r="O40" t="str">
-        <x:v>`"asha.example.com"`</x:v>
+        <x:v>A fourth variable is required because `split` returns one comma character as an extra value in addition to the three fields</x:v>
       </x:c>
       <x:c r="P40" t="str">
-        <x:v>`"@.com"`</x:v>
+        <x:v>Joining the result with commas before unpacking would preserve four separate values while making three variables sufficient</x:v>
       </x:c>
       <x:c r="Q40" t="n">
-        <x:v>4</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="41" ht="39.599998474121094" hidden="0" customHeight="1">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41" ht="171.60000610351562" hidden="0" customHeight="1">
       <x:c r="A41" t="str">
-        <x:v>Python - MCQ - 5.2.30</x:v>
+        <x:v>Python - MCQ - 5.4.10</x:v>
       </x:c>
       <x:c r="B41" t="str">
-        <x:v>A content-analytics tool must clean text once, count words and non-space characters, and perform a case-insensitive search.
-A tool must trim input, normalise case, count words, count non-space characters, and perform a case-insensitive keyword check. Approve the control plan.</x:v>
+        <x:v>Summarising a cleaned campaign message
+A campaign analyzer runs:
+```python
+message = "  Python, python makes TEXT fun  "
+clean = message.strip().lower().replace(",", "")
+words = clean.split()
+python_mentions = clean.count("python")
+summary = f"{len(words)} words | python={python_mentions}"
+```
+Which summary is generated after the full pipeline?</x:v>
       </x:c>
       <x:c r="C41" t="str">
-        <x:v>The pipeline cleans once, then applies the appropriate splitting, replacement, length, and membership tools to the normalised text.</x:v>
+        <x:v>Cleaning produces five words, and the lowercase text contains two occurrences of `python`.</x:v>
       </x:c>
       <x:c r="D41" t="n">
-        <x:v>8</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E41" t="str">
         <x:v>published</x:v>
       </x:c>
       <x:c r="F41" t="str">
-        <x:v>medium</x:v>
+        <x:v>hard</x:v>
       </x:c>
       <x:c r="G41" t="str">
-        <x:v>evaluate</x:v>
+        <x:v>apply</x:v>
       </x:c>
       <x:c r="H41" t="str">
-        <x:v>python - Set 2</x:v>
+        <x:v>python - Set 4</x:v>
       </x:c>
       <x:c r="I41" t="str">
         <x:v>python</x:v>
@@ -2607,19 +2599,20 @@
       </x:c>
       <x:c r="L41"/>
       <x:c r="M41" t="str">
-        <x:v>Search the raw input first and never store cleaned text.</x:v>
+        <x:v>`"6 words | python=1"`</x:v>
       </x:c>
       <x:c r="N41" t="str">
-        <x:v>Store `clean = raw.strip().lower()`, use `len(clean.split())`, use `len(clean.replace(" ", ""))`, and test the lowercased keyword with `in`.</x:v>
+        <x:v>`"5 words | python=1"`</x:v>
       </x:c>
       <x:c r="O41" t="str">
-        <x:v>Convert the sentence to an integer and then split it.</x:v>
+        <x:v>`"6 words | python=2"`</x:v>
       </x:c>
       <x:c r="P41" t="str">
-        <x:v>Use `index()` for every search and assume the keyword exists.</x:v>
+        <x:v>`"5 words | python=2"`
+---</x:v>
       </x:c>
       <x:c r="Q41" t="n">
-        <x:v>2</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
